--- a/marksheet.xlsx
+++ b/marksheet.xlsx
@@ -5,22 +5,33 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SOURAV TRADERS\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SOURAV TRADERS\Desktop\New folder\Study-Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4EE2095-D6F6-43D5-AAF4-894F507807B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEEE3C0-5158-45E7-A658-8357CAA914DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DataBase" sheetId="1" r:id="rId1"/>
     <sheet name="Rating" sheetId="2" r:id="rId2"/>
     <sheet name="ReportCard" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -30,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="66">
   <si>
     <t>Roll</t>
   </si>
@@ -135,13 +146,106 @@
   </si>
   <si>
     <t>Najmul Islam</t>
+  </si>
+  <si>
+    <t>Star Rating</t>
+  </si>
+  <si>
+    <t>Not Satisfactory</t>
+  </si>
+  <si>
+    <t>Satisfactory</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Very Good</t>
+  </si>
+  <si>
+    <t>Execllent</t>
+  </si>
+  <si>
+    <t>Marks Range</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>90-100</t>
+  </si>
+  <si>
+    <t>81-90</t>
+  </si>
+  <si>
+    <t>71-80</t>
+  </si>
+  <si>
+    <t>61-70</t>
+  </si>
+  <si>
+    <t>51-60</t>
+  </si>
+  <si>
+    <t>41-50</t>
+  </si>
+  <si>
+    <t>33-40</t>
+  </si>
+  <si>
+    <t>Below 33</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>A-</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Minium Marks</t>
+  </si>
+  <si>
+    <t>AGROJATRA SHISHU BIKASH SCHOOL</t>
+  </si>
+  <si>
+    <t>(An Ideal School, Affiliated to NCTB,Dhaka)</t>
+  </si>
+  <si>
+    <t>Dokkhin Kanial Khata ,Boiragi Para, Nilphamari Sadar, Nilphamari</t>
+  </si>
+  <si>
+    <t>www.agrojatrashishubikashschool.com</t>
+  </si>
+  <si>
+    <t>Affilation Number:7725</t>
+  </si>
+  <si>
+    <t>School Number:25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,16 +253,72 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -166,14 +326,160 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -187,6 +493,77 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>581026</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{771A2C04-1252-27FB-510B-805416FF7208}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="581026" y="161925"/>
+          <a:ext cx="8772524" cy="9782175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -457,15 +834,15 @@
   <cols>
     <col min="1" max="1" width="4.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="5.42578125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8.140625" bestFit="1" customWidth="1"/>
@@ -657,6 +1034,27 @@
       <c r="F6">
         <v>5</v>
       </c>
+      <c r="I6">
+        <v>98</v>
+      </c>
+      <c r="J6">
+        <v>99</v>
+      </c>
+      <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="L6">
+        <v>98</v>
+      </c>
+      <c r="M6">
+        <v>99</v>
+      </c>
+      <c r="N6">
+        <v>97</v>
+      </c>
+      <c r="O6">
+        <v>48</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -668,6 +1066,27 @@
       <c r="F7">
         <v>5</v>
       </c>
+      <c r="I7">
+        <v>88</v>
+      </c>
+      <c r="J7">
+        <v>98</v>
+      </c>
+      <c r="K7">
+        <v>99</v>
+      </c>
+      <c r="L7">
+        <v>97</v>
+      </c>
+      <c r="M7">
+        <v>98</v>
+      </c>
+      <c r="N7">
+        <v>88</v>
+      </c>
+      <c r="O7">
+        <v>45</v>
+      </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -679,6 +1098,27 @@
       <c r="F8">
         <v>5</v>
       </c>
+      <c r="I8">
+        <v>96</v>
+      </c>
+      <c r="J8">
+        <v>98</v>
+      </c>
+      <c r="K8">
+        <v>99</v>
+      </c>
+      <c r="L8">
+        <v>98</v>
+      </c>
+      <c r="M8">
+        <v>87</v>
+      </c>
+      <c r="N8">
+        <v>88</v>
+      </c>
+      <c r="O8">
+        <v>45</v>
+      </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -690,6 +1130,27 @@
       <c r="F9">
         <v>5</v>
       </c>
+      <c r="I9">
+        <v>87</v>
+      </c>
+      <c r="J9">
+        <v>90</v>
+      </c>
+      <c r="K9">
+        <v>88</v>
+      </c>
+      <c r="L9">
+        <v>84</v>
+      </c>
+      <c r="M9">
+        <v>87</v>
+      </c>
+      <c r="N9">
+        <v>85</v>
+      </c>
+      <c r="O9">
+        <v>45</v>
+      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -701,6 +1162,27 @@
       <c r="F10">
         <v>5</v>
       </c>
+      <c r="I10">
+        <v>90</v>
+      </c>
+      <c r="J10">
+        <v>98</v>
+      </c>
+      <c r="K10">
+        <v>95</v>
+      </c>
+      <c r="L10">
+        <v>92</v>
+      </c>
+      <c r="M10">
+        <v>90</v>
+      </c>
+      <c r="N10">
+        <v>85</v>
+      </c>
+      <c r="O10">
+        <v>45</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
@@ -712,6 +1194,27 @@
       <c r="F11">
         <v>5</v>
       </c>
+      <c r="I11">
+        <v>87</v>
+      </c>
+      <c r="J11">
+        <v>98</v>
+      </c>
+      <c r="K11">
+        <v>95</v>
+      </c>
+      <c r="L11">
+        <v>92</v>
+      </c>
+      <c r="M11">
+        <v>98</v>
+      </c>
+      <c r="N11">
+        <v>85</v>
+      </c>
+      <c r="O11">
+        <v>45</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
@@ -723,6 +1226,27 @@
       <c r="F12">
         <v>5</v>
       </c>
+      <c r="I12">
+        <v>80</v>
+      </c>
+      <c r="J12">
+        <v>85</v>
+      </c>
+      <c r="K12">
+        <v>80</v>
+      </c>
+      <c r="L12">
+        <v>84</v>
+      </c>
+      <c r="M12">
+        <v>80</v>
+      </c>
+      <c r="N12">
+        <v>82</v>
+      </c>
+      <c r="O12">
+        <v>45</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
@@ -734,6 +1258,27 @@
       <c r="F13">
         <v>5</v>
       </c>
+      <c r="I13">
+        <v>82</v>
+      </c>
+      <c r="J13">
+        <v>98</v>
+      </c>
+      <c r="K13">
+        <v>85</v>
+      </c>
+      <c r="L13">
+        <v>80</v>
+      </c>
+      <c r="M13">
+        <v>90</v>
+      </c>
+      <c r="N13">
+        <v>87</v>
+      </c>
+      <c r="O13">
+        <v>45</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
@@ -745,6 +1290,27 @@
       <c r="F14">
         <v>5</v>
       </c>
+      <c r="I14">
+        <v>85</v>
+      </c>
+      <c r="J14">
+        <v>85</v>
+      </c>
+      <c r="K14">
+        <v>88</v>
+      </c>
+      <c r="L14">
+        <v>83</v>
+      </c>
+      <c r="M14">
+        <v>95</v>
+      </c>
+      <c r="N14">
+        <v>85</v>
+      </c>
+      <c r="O14">
+        <v>45</v>
+      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -756,6 +1322,27 @@
       <c r="F15">
         <v>5</v>
       </c>
+      <c r="I15">
+        <v>80</v>
+      </c>
+      <c r="J15">
+        <v>80</v>
+      </c>
+      <c r="K15">
+        <v>75</v>
+      </c>
+      <c r="L15">
+        <v>80</v>
+      </c>
+      <c r="M15">
+        <v>80</v>
+      </c>
+      <c r="N15">
+        <v>81</v>
+      </c>
+      <c r="O15">
+        <v>40</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
@@ -767,8 +1354,29 @@
       <c r="F16">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I16">
+        <v>80</v>
+      </c>
+      <c r="J16">
+        <v>82</v>
+      </c>
+      <c r="K16">
+        <v>83</v>
+      </c>
+      <c r="L16">
+        <v>80</v>
+      </c>
+      <c r="M16">
+        <v>80</v>
+      </c>
+      <c r="N16">
+        <v>82</v>
+      </c>
+      <c r="O16">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -778,8 +1386,29 @@
       <c r="F17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I17">
+        <v>80</v>
+      </c>
+      <c r="J17">
+        <v>90</v>
+      </c>
+      <c r="K17">
+        <v>85</v>
+      </c>
+      <c r="L17">
+        <v>82</v>
+      </c>
+      <c r="M17">
+        <v>94</v>
+      </c>
+      <c r="N17">
+        <v>84</v>
+      </c>
+      <c r="O17">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -789,8 +1418,29 @@
       <c r="F18">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I18">
+        <v>80</v>
+      </c>
+      <c r="J18">
+        <v>80</v>
+      </c>
+      <c r="K18">
+        <v>82</v>
+      </c>
+      <c r="L18">
+        <v>80</v>
+      </c>
+      <c r="M18">
+        <v>83</v>
+      </c>
+      <c r="N18">
+        <v>80</v>
+      </c>
+      <c r="O18">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -800,8 +1450,29 @@
       <c r="F19">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I19">
+        <v>80</v>
+      </c>
+      <c r="J19">
+        <v>80</v>
+      </c>
+      <c r="K19">
+        <v>85</v>
+      </c>
+      <c r="L19">
+        <v>80</v>
+      </c>
+      <c r="M19">
+        <v>82</v>
+      </c>
+      <c r="N19">
+        <v>80</v>
+      </c>
+      <c r="O19">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -811,8 +1482,29 @@
       <c r="F20">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I20">
+        <v>85</v>
+      </c>
+      <c r="J20">
+        <v>80</v>
+      </c>
+      <c r="K20">
+        <v>75</v>
+      </c>
+      <c r="L20">
+        <v>64</v>
+      </c>
+      <c r="M20">
+        <v>76</v>
+      </c>
+      <c r="N20">
+        <v>80</v>
+      </c>
+      <c r="O20">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -821,6 +1513,27 @@
       </c>
       <c r="F21">
         <v>5</v>
+      </c>
+      <c r="I21">
+        <v>80</v>
+      </c>
+      <c r="J21">
+        <v>75</v>
+      </c>
+      <c r="K21">
+        <v>65</v>
+      </c>
+      <c r="L21">
+        <v>65</v>
+      </c>
+      <c r="M21">
+        <v>80</v>
+      </c>
+      <c r="N21">
+        <v>80</v>
+      </c>
+      <c r="O21">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -830,18 +1543,1091 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CD00566-86F0-4F03-8BBF-95429FC821FB}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:F18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="4"/>
+    <col min="2" max="2" width="12.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="4"/>
+    <col min="4" max="4" width="15.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C3" s="7">
+        <v>1</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="6"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C4" s="7">
+        <v>2</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="6"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C5" s="7">
+        <v>3</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C6" s="7">
+        <v>4</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C7" s="7">
+        <v>5</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="7">
+        <v>33</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="7">
+        <v>41</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="7">
+        <v>51</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="7">
+        <v>61</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="7">
+        <v>71</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="7">
+        <v>81</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="7">
+        <v>91</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C2:D2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8DF2A12-82DF-4235-887F-EDAFE42B2966}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:P52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="6.140625" customWidth="1"/>
+    <col min="16" max="16" width="6.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="10"/>
+    </row>
+    <row r="3" spans="2:16" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="11"/>
+      <c r="C3" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="12"/>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B4" s="11"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="12"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B5" s="11"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="12"/>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B6" s="11"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="12"/>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B7" s="11"/>
+      <c r="P7" s="12"/>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B8" s="11"/>
+      <c r="C8" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="12"/>
+    </row>
+    <row r="9" spans="2:16" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="21"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="23"/>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B10" s="11"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="12"/>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B11" s="11"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="12"/>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B12" s="11"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="12"/>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B13" s="11"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="12"/>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B14" s="11"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="12"/>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B15" s="11"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="12"/>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B16" s="11"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="12"/>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B17" s="11"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="12"/>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="12"/>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="12"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B20" s="11"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="12"/>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B21" s="11"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="12"/>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B22" s="11"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="12"/>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B23" s="11"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="12"/>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B24" s="11"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="12"/>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B25" s="11"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="12"/>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B26" s="11"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="12"/>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B27" s="11"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="12"/>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B28" s="11"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="12"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B29" s="11"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="12"/>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B30" s="11"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="12"/>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B31" s="11"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="12"/>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B32" s="11"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="12"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B33" s="11"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="12"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B34" s="11"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="12"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B35" s="11"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="12"/>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B36" s="11"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="12"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B37" s="11"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="12"/>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B38" s="11"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="12"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B39" s="11"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="12"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B40" s="11"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="12"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B41" s="11"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="12"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B42" s="11"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="12"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B43" s="11"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="12"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B44" s="11"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" s="12"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B45" s="11"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" s="12"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B46" s="11"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" s="12"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B47" s="11"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" s="12"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B48" s="11"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" s="12"/>
+    </row>
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B49" s="11"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" s="12"/>
+    </row>
+    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B50" s="11"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="12"/>
+    </row>
+    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B51" s="11"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" s="12"/>
+    </row>
+    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B52" s="13"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="14"/>
+      <c r="M52" s="14"/>
+      <c r="N52" s="14"/>
+      <c r="O52" s="14"/>
+      <c r="P52" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C3:O3"/>
+    <mergeCell ref="D4:N4"/>
+    <mergeCell ref="E5:M5"/>
+    <mergeCell ref="D6:N6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D6" r:id="rId1" xr:uid="{02A21183-A0C8-4D99-B719-FFA62D55BA23}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/marksheet.xlsx
+++ b/marksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atosh\OneDrive\Desktop\Study-Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46594C19-E2AD-4F22-B8BA-37E8B655E9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9BCEE8-4BBB-4D76-8009-D434DB5DA315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,47 +41,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="129">
   <si>
     <t>BGS</t>
   </si>
   <si>
-    <t>Khushi Roy</t>
-  </si>
-  <si>
-    <t>Joya Roy</t>
-  </si>
-  <si>
     <t>Imran Islam</t>
   </si>
   <si>
-    <t>Osman Ali</t>
-  </si>
-  <si>
-    <t>Sristi Roy</t>
-  </si>
-  <si>
-    <t>Sumaiya Akther</t>
-  </si>
-  <si>
-    <t>Sharabonti Roy</t>
-  </si>
-  <si>
     <t>Sathi Sharma</t>
   </si>
   <si>
-    <t>Kulsum Akther</t>
-  </si>
-  <si>
-    <t>Nuri Akther</t>
-  </si>
-  <si>
     <t>Rabbi Islam</t>
   </si>
   <si>
-    <t>Pushpita Roy</t>
-  </si>
-  <si>
     <t>Mijan Islam</t>
   </si>
   <si>
@@ -223,15 +196,6 @@
     <t>ADDRESS</t>
   </si>
   <si>
-    <t>NURNOBI</t>
-  </si>
-  <si>
-    <t>KADIJA</t>
-  </si>
-  <si>
-    <t>PORAPARA</t>
-  </si>
-  <si>
     <t>CLASS</t>
   </si>
   <si>
@@ -308,6 +272,162 @@
   </si>
   <si>
     <t>PASS/FAIL</t>
+  </si>
+  <si>
+    <t>STUDENT'S BEHAVIOUR</t>
+  </si>
+  <si>
+    <t>REMARKS OF STARS</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Attendance</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Overall Grade</t>
+  </si>
+  <si>
+    <t>Khushimoni roy</t>
+  </si>
+  <si>
+    <t>Atul Chandro Roy</t>
+  </si>
+  <si>
+    <t>Sreemoty Ganga Rani</t>
+  </si>
+  <si>
+    <t>01763299043</t>
+  </si>
+  <si>
+    <t>Jaya Rani</t>
+  </si>
+  <si>
+    <t>Sreemoty Trisna Rani</t>
+  </si>
+  <si>
+    <t>Sree Narayan Roy</t>
+  </si>
+  <si>
+    <t>01326026347</t>
+  </si>
+  <si>
+    <t>Md Osman Goni</t>
+  </si>
+  <si>
+    <t>Omar Faruk</t>
+  </si>
+  <si>
+    <t>Roksana Begum</t>
+  </si>
+  <si>
+    <t>Nuri Akter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nur Mohammad </t>
+  </si>
+  <si>
+    <t>Mrs. Nasima Begum</t>
+  </si>
+  <si>
+    <t>Kanial Khata Cinirkuti Bazar</t>
+  </si>
+  <si>
+    <t>Kanial Khata Munsipara</t>
+  </si>
+  <si>
+    <t>Kanial Khata Porapara</t>
+  </si>
+  <si>
+    <t>01346468836</t>
+  </si>
+  <si>
+    <t>Mst Umma Kulsum</t>
+  </si>
+  <si>
+    <t>Nurnabi</t>
+  </si>
+  <si>
+    <t>Mst. Mahmuda Khatun</t>
+  </si>
+  <si>
+    <t>Kanialkhata</t>
+  </si>
+  <si>
+    <t>01706807154</t>
+  </si>
+  <si>
+    <t>Dayal Shel</t>
+  </si>
+  <si>
+    <t>Maloti Rani</t>
+  </si>
+  <si>
+    <t>Kanial Khata Boiragi Para</t>
+  </si>
+  <si>
+    <t>01313934352</t>
+  </si>
+  <si>
+    <t>Anamika Rani Roy</t>
+  </si>
+  <si>
+    <t>Santos Kumar Ray</t>
+  </si>
+  <si>
+    <t>Vagirathi Rany</t>
+  </si>
+  <si>
+    <t>DOKKHIN KANIAL KHATA MASTAR PARA</t>
+  </si>
+  <si>
+    <t>01326025653</t>
+  </si>
+  <si>
+    <t>Sumaiya Islam</t>
+  </si>
+  <si>
+    <t>Md Robiul Islam</t>
+  </si>
+  <si>
+    <t>Mst Rashida Begum</t>
+  </si>
+  <si>
+    <t>01768842049</t>
+  </si>
+  <si>
+    <t>SHRABONTI ROY</t>
+  </si>
+  <si>
+    <t>NARESH CHANDRA ROY</t>
+  </si>
+  <si>
+    <t>JANATA RANI ROY</t>
+  </si>
+  <si>
+    <t>KANIAL KHATA PONDIT PARA</t>
+  </si>
+  <si>
+    <t>01753277584</t>
+  </si>
+  <si>
+    <t>SISTY RANI ROY</t>
+  </si>
+  <si>
+    <t>SAPON KUMAR ROY</t>
+  </si>
+  <si>
+    <t>LAKKHI RANI</t>
+  </si>
+  <si>
+    <t>01726759389</t>
   </si>
 </sst>
 </file>
@@ -315,9 +435,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="@\ * \:"/>
+    <numFmt numFmtId="164" formatCode="@\ * \:"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -332,12 +452,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="24"/>
-      <color rgb="FF00B050"/>
-      <name val="Arial Black"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -387,7 +501,28 @@
     <font>
       <b/>
       <u/>
-      <sz val="11"/>
+      <sz val="14"/>
+      <color theme="5"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="4" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -395,14 +530,54 @@
     </font>
     <font>
       <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="7" tint="0.59999389629810485"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF002060"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <u/>
-      <sz val="14"/>
-      <color theme="5"/>
-      <name val="Arial Black"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -430,6 +605,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -577,10 +764,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -601,92 +788,172 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -772,6 +1039,156 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>106716</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A25357C-6FE7-A7E9-E83A-B8B0205F59DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="352425" y="390525"/>
+          <a:ext cx="923925" cy="906816"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>323849</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>26288</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>124781</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30497364-324C-E903-9125-6E49AA625961}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7324724" y="428625"/>
+          <a:ext cx="921639" cy="886781"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>156891</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01C7779C-699A-9F16-8B8B-C6656397857B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="762000" y="9553575"/>
+          <a:ext cx="7772400" cy="1014141"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1040,11 +1457,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8DF2A12-82DF-4235-887F-EDAFE42B2966}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:P52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="2.140625" customWidth="1"/>
+    <col min="12" max="12" width="6.42578125" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" customWidth="1"/>
     <col min="16" max="16" width="2.140625" customWidth="1"/>
+    <col min="17" max="17" width="0.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
@@ -1064,41 +1488,41 @@
       <c r="O2" s="7"/>
       <c r="P2" s="8"/>
     </row>
-    <row r="3" spans="2:16" ht="36.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:16" ht="33.75" x14ac:dyDescent="0.25">
       <c r="B3" s="9"/>
-      <c r="C3" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
+      <c r="C3" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
       <c r="P3" s="10"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B4" s="9"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
+      <c r="D4" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
       <c r="O4" s="1"/>
       <c r="P4" s="10"/>
     </row>
@@ -1106,17 +1530,17 @@
       <c r="B5" s="9"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
+      <c r="E5" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="10"/>
@@ -1124,19 +1548,19 @@
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="9"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
+      <c r="D6" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
       <c r="O6" s="2"/>
       <c r="P6" s="10"/>
     </row>
@@ -1146,11 +1570,11 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" s="9"/>
-      <c r="C8" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
+      <c r="C8" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1158,11 +1582,11 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
-      <c r="M8" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
+      <c r="M8" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
       <c r="P8" s="10"/>
     </row>
     <row r="9" spans="2:16" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1182,145 +1606,145 @@
       <c r="O9" s="15"/>
       <c r="P9" s="16"/>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="9"/>
-      <c r="C10" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="24"/>
+      <c r="C10" s="74" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="75"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="75"/>
+      <c r="K10" s="75"/>
+      <c r="L10" s="75"/>
+      <c r="M10" s="75"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="75"/>
       <c r="P10" s="10"/>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="9"/>
-      <c r="C11" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="24"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="24"/>
+      <c r="C11" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="75"/>
+      <c r="K11" s="75"/>
+      <c r="L11" s="75"/>
+      <c r="M11" s="75"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="75"/>
       <c r="P11" s="10"/>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B12" s="9"/>
-      <c r="C12" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
+      <c r="C12" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="75"/>
+      <c r="K12" s="75"/>
+      <c r="L12" s="75"/>
+      <c r="M12" s="75"/>
+      <c r="N12" s="75"/>
+      <c r="O12" s="75"/>
       <c r="P12" s="10"/>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="9"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="77"/>
+      <c r="M13" s="77"/>
+      <c r="N13" s="77"/>
+      <c r="O13" s="77"/>
       <c r="P13" s="10"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B14" s="9"/>
-      <c r="C14" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="31">
-        <v>6</v>
-      </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
+      <c r="C14" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="31"/>
+      <c r="E14" s="33">
+        <v>10</v>
+      </c>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
-      <c r="K14" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="L14" s="29"/>
-      <c r="M14" s="28">
+      <c r="K14" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="L14" s="31"/>
+      <c r="M14" s="73">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!K14,DataBase!$A$1:$O$1,0),0)</f>
         <v>5</v>
       </c>
-      <c r="N14" s="28"/>
-      <c r="O14" s="28"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="73"/>
       <c r="P14" s="10"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B15" s="9"/>
-      <c r="C15" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="29"/>
-      <c r="E15" s="28" t="str">
+      <c r="C15" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="31"/>
+      <c r="E15" s="34" t="str">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!C15,DataBase!$A$1:$O$1,0),0)</f>
-        <v>Sristi Roy</v>
-      </c>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
+        <v>Nuri Akter</v>
+      </c>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
-      <c r="K15" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="L15" s="29"/>
-      <c r="M15" s="28">
+      <c r="K15" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="31"/>
+      <c r="M15" s="34" t="str">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!K15,DataBase!$A$1:$O$1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="N15" s="28"/>
-      <c r="O15" s="28"/>
+        <v>01346468836</v>
+      </c>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
       <c r="P15" s="10"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B16" s="9"/>
-      <c r="C16" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="29"/>
-      <c r="E16" s="28">
+      <c r="C16" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="31"/>
+      <c r="E16" s="34" t="str">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!C16,DataBase!$A$1:$O$1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
+        <v xml:space="preserve">Nur Mohammad </v>
+      </c>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1333,16 +1757,16 @@
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B17" s="9"/>
-      <c r="C17" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="30"/>
-      <c r="E17" s="28">
+      <c r="C17" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="32"/>
+      <c r="E17" s="34" t="str">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!C17,DataBase!$A$1:$O$1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
+        <v>Mrs. Nasima Begum</v>
+      </c>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1355,16 +1779,16 @@
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B18" s="9"/>
-      <c r="C18" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="30"/>
-      <c r="E18" s="28">
+      <c r="C18" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="32"/>
+      <c r="E18" s="34" t="str">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!C18,DataBase!$A$1:$O$1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
+        <v>Kanial Khata Munsipara</v>
+      </c>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -1394,337 +1818,337 @@
     </row>
     <row r="20" spans="2:16" ht="23.25" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B20" s="9"/>
-      <c r="C20" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
-      <c r="N20" s="32"/>
-      <c r="O20" s="32"/>
+      <c r="C20" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
       <c r="P20" s="10"/>
     </row>
     <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="9"/>
-      <c r="C21" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="34"/>
+      <c r="C21" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="47"/>
+      <c r="K21" s="47"/>
+      <c r="L21" s="47"/>
+      <c r="M21" s="47"/>
+      <c r="N21" s="47"/>
+      <c r="O21" s="48"/>
       <c r="P21" s="10"/>
     </row>
     <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="9"/>
-      <c r="C22" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="F22" s="41"/>
-      <c r="G22" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="H22" s="41"/>
-      <c r="I22" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="J22" s="41"/>
-      <c r="K22" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="L22" s="41"/>
-      <c r="M22" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="N22" s="46"/>
-      <c r="O22" s="41"/>
+      <c r="C22" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="30"/>
+      <c r="E22" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" s="22"/>
+      <c r="G22" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22" s="22"/>
+      <c r="I22" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="J22" s="22"/>
+      <c r="K22" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="L22" s="22"/>
+      <c r="M22" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="N22" s="21"/>
+      <c r="O22" s="22"/>
       <c r="P22" s="10"/>
     </row>
     <row r="23" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="9"/>
-      <c r="C23" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="43"/>
-      <c r="E23" s="38">
+      <c r="C23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="27"/>
+      <c r="E23" s="18">
         <v>100</v>
       </c>
-      <c r="F23" s="39"/>
-      <c r="G23" s="38">
+      <c r="F23" s="19"/>
+      <c r="G23" s="18">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C23,DataBase!$A$1:$O$1,0),0)</f>
-        <v>88</v>
-      </c>
-      <c r="H23" s="39"/>
-      <c r="I23" s="44">
+        <v>87</v>
+      </c>
+      <c r="H23" s="19"/>
+      <c r="I23" s="24">
         <f>G23/E23</f>
-        <v>0.88</v>
-      </c>
-      <c r="J23" s="45"/>
-      <c r="K23" s="38" t="str">
+        <v>0.87</v>
+      </c>
+      <c r="J23" s="25"/>
+      <c r="K23" s="18" t="str">
         <f>LOOKUP(G23,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
         <v>A</v>
       </c>
-      <c r="L23" s="39"/>
-      <c r="M23" s="38" t="str">
+      <c r="L23" s="19"/>
+      <c r="M23" s="18" t="str">
         <f>IF(I23&lt;0.33,"FAIL","PASS")</f>
         <v>PASS</v>
       </c>
-      <c r="N23" s="47"/>
-      <c r="O23" s="39"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="19"/>
       <c r="P23" s="10"/>
     </row>
     <row r="24" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="9"/>
-      <c r="C24" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="43"/>
-      <c r="E24" s="38">
+      <c r="C24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="27"/>
+      <c r="E24" s="18">
         <v>100</v>
       </c>
-      <c r="F24" s="39"/>
-      <c r="G24" s="38">
+      <c r="F24" s="19"/>
+      <c r="G24" s="18">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C24,DataBase!$A$1:$O$1,0),0)</f>
         <v>98</v>
       </c>
-      <c r="H24" s="39"/>
-      <c r="I24" s="44">
+      <c r="H24" s="19"/>
+      <c r="I24" s="24">
         <f t="shared" ref="I24:I29" si="0">G24/E24</f>
         <v>0.98</v>
       </c>
-      <c r="J24" s="45"/>
-      <c r="K24" s="38" t="str">
+      <c r="J24" s="25"/>
+      <c r="K24" s="18" t="str">
         <f>LOOKUP(G24,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
         <v>A+</v>
       </c>
-      <c r="L24" s="39"/>
-      <c r="M24" s="38" t="str">
+      <c r="L24" s="19"/>
+      <c r="M24" s="18" t="str">
         <f t="shared" ref="M24:M29" si="1">IF(I24&lt;0.33,"FAIL","PASS")</f>
         <v>PASS</v>
       </c>
-      <c r="N24" s="47"/>
-      <c r="O24" s="39"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="19"/>
       <c r="P24" s="10"/>
     </row>
     <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="9"/>
-      <c r="C25" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" s="43"/>
-      <c r="E25" s="38">
+      <c r="C25" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="27"/>
+      <c r="E25" s="18">
         <v>100</v>
       </c>
-      <c r="F25" s="39"/>
-      <c r="G25" s="38">
+      <c r="F25" s="19"/>
+      <c r="G25" s="18">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C25,DataBase!$A$1:$O$1,0),0)</f>
-        <v>99</v>
-      </c>
-      <c r="H25" s="39"/>
-      <c r="I25" s="44">
+        <v>95</v>
+      </c>
+      <c r="H25" s="19"/>
+      <c r="I25" s="24">
         <f t="shared" si="0"/>
-        <v>0.99</v>
-      </c>
-      <c r="J25" s="45"/>
-      <c r="K25" s="38" t="str">
+        <v>0.95</v>
+      </c>
+      <c r="J25" s="25"/>
+      <c r="K25" s="18" t="str">
         <f>LOOKUP(G25,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
         <v>A+</v>
       </c>
-      <c r="L25" s="39"/>
-      <c r="M25" s="38" t="str">
+      <c r="L25" s="19"/>
+      <c r="M25" s="18" t="str">
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="N25" s="47"/>
-      <c r="O25" s="39"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="19"/>
       <c r="P25" s="10"/>
     </row>
     <row r="26" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="9"/>
-      <c r="C26" s="42" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="43"/>
-      <c r="E26" s="38">
+      <c r="C26" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="27"/>
+      <c r="E26" s="18">
         <v>100</v>
       </c>
-      <c r="F26" s="39"/>
-      <c r="G26" s="38">
+      <c r="F26" s="19"/>
+      <c r="G26" s="18">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C26,DataBase!$A$1:$O$1,0),0)</f>
-        <v>97</v>
-      </c>
-      <c r="H26" s="39"/>
-      <c r="I26" s="44">
+        <v>92</v>
+      </c>
+      <c r="H26" s="19"/>
+      <c r="I26" s="24">
         <f t="shared" si="0"/>
-        <v>0.97</v>
-      </c>
-      <c r="J26" s="45"/>
-      <c r="K26" s="38" t="str">
+        <v>0.92</v>
+      </c>
+      <c r="J26" s="25"/>
+      <c r="K26" s="18" t="str">
         <f>LOOKUP(G26,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
         <v>A+</v>
       </c>
-      <c r="L26" s="39"/>
-      <c r="M26" s="38" t="str">
+      <c r="L26" s="19"/>
+      <c r="M26" s="18" t="str">
+        <f>IF(I26&lt;0.33,"FAIL","PASS")</f>
+        <v>PASS</v>
+      </c>
+      <c r="N26" s="23"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="10"/>
+    </row>
+    <row r="27" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="9"/>
+      <c r="C27" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="D27" s="27"/>
+      <c r="E27" s="18">
+        <v>100</v>
+      </c>
+      <c r="F27" s="19"/>
+      <c r="G27" s="18">
+        <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C27,DataBase!$A$1:$O$1,0),0)</f>
+        <v>98</v>
+      </c>
+      <c r="H27" s="19"/>
+      <c r="I27" s="24">
+        <f t="shared" si="0"/>
+        <v>0.98</v>
+      </c>
+      <c r="J27" s="25"/>
+      <c r="K27" s="18" t="str">
+        <f>LOOKUP(G27,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
+        <v>A+</v>
+      </c>
+      <c r="L27" s="19"/>
+      <c r="M27" s="18" t="str">
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="N26" s="47"/>
-      <c r="O26" s="39"/>
-      <c r="P26" s="10"/>
-    </row>
-    <row r="27" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="9"/>
-      <c r="C27" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="D27" s="43"/>
-      <c r="E27" s="38">
+      <c r="N27" s="23"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="10"/>
+    </row>
+    <row r="28" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="9"/>
+      <c r="C28" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="27"/>
+      <c r="E28" s="18">
         <v>100</v>
       </c>
-      <c r="F27" s="39"/>
-      <c r="G27" s="38">
-        <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C27,DataBase!$A$1:$O$1,0),0)</f>
-        <v>98</v>
-      </c>
-      <c r="H27" s="39"/>
-      <c r="I27" s="44">
+      <c r="F28" s="19"/>
+      <c r="G28" s="18">
+        <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C28,DataBase!$A$1:$O$1,0),0)</f>
+        <v>85</v>
+      </c>
+      <c r="H28" s="19"/>
+      <c r="I28" s="24">
         <f t="shared" si="0"/>
-        <v>0.98</v>
-      </c>
-      <c r="J27" s="45"/>
-      <c r="K27" s="38" t="str">
-        <f>LOOKUP(G27,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
-        <v>A+</v>
-      </c>
-      <c r="L27" s="39"/>
-      <c r="M27" s="38" t="str">
+        <v>0.85</v>
+      </c>
+      <c r="J28" s="25"/>
+      <c r="K28" s="18" t="str">
+        <f>LOOKUP(G28,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
+        <v>A</v>
+      </c>
+      <c r="L28" s="19"/>
+      <c r="M28" s="18" t="str">
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="N27" s="47"/>
-      <c r="O27" s="39"/>
-      <c r="P27" s="10"/>
-    </row>
-    <row r="28" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="9"/>
-      <c r="C28" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="D28" s="43"/>
-      <c r="E28" s="38">
-        <v>100</v>
-      </c>
-      <c r="F28" s="39"/>
-      <c r="G28" s="38">
-        <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C28,DataBase!$A$1:$O$1,0),0)</f>
-        <v>88</v>
-      </c>
-      <c r="H28" s="39"/>
-      <c r="I28" s="44">
+      <c r="N28" s="23"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="10"/>
+    </row>
+    <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="9"/>
+      <c r="C29" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="27"/>
+      <c r="E29" s="18">
+        <v>50</v>
+      </c>
+      <c r="F29" s="19"/>
+      <c r="G29" s="18">
+        <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C29,DataBase!$A$1:$O$1,0),0)</f>
+        <v>45</v>
+      </c>
+      <c r="H29" s="19"/>
+      <c r="I29" s="24">
         <f t="shared" si="0"/>
-        <v>0.88</v>
-      </c>
-      <c r="J28" s="45"/>
-      <c r="K28" s="38" t="str">
-        <f>LOOKUP(G28,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
-        <v>A</v>
-      </c>
-      <c r="L28" s="39"/>
-      <c r="M28" s="38" t="str">
+        <v>0.9</v>
+      </c>
+      <c r="J29" s="25"/>
+      <c r="K29" s="18" t="str">
+        <f>LOOKUP(G29,Rating!$K$11:$K$18,Rating!$L$11:$L$18)</f>
+        <v>A+</v>
+      </c>
+      <c r="L29" s="19"/>
+      <c r="M29" s="18" t="str">
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="N28" s="47"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="10"/>
-    </row>
-    <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="9"/>
-      <c r="C29" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" s="43"/>
-      <c r="E29" s="38">
-        <v>50</v>
-      </c>
-      <c r="F29" s="39"/>
-      <c r="G29" s="38">
-        <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C29,DataBase!$A$1:$O$1,0),0)</f>
-        <v>45</v>
-      </c>
-      <c r="H29" s="39"/>
-      <c r="I29" s="44">
-        <f t="shared" si="0"/>
-        <v>0.9</v>
-      </c>
-      <c r="J29" s="45"/>
-      <c r="K29" s="38" t="str">
-        <f>LOOKUP(G29,Rating!$K$11:$K$18,Rating!$L$11:$L$18)</f>
-        <v>A+</v>
-      </c>
-      <c r="L29" s="39"/>
-      <c r="M29" s="38" t="str">
-        <f t="shared" si="1"/>
-        <v>PASS</v>
-      </c>
-      <c r="N29" s="47"/>
-      <c r="O29" s="39"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="19"/>
       <c r="P29" s="10"/>
     </row>
     <row r="30" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="9"/>
-      <c r="C30" s="42" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" s="43"/>
-      <c r="E30" s="38">
+      <c r="C30" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" s="27"/>
+      <c r="E30" s="18">
         <f>SUM(E23:F29)</f>
         <v>650</v>
       </c>
-      <c r="F30" s="39"/>
-      <c r="G30" s="38">
+      <c r="F30" s="19"/>
+      <c r="G30" s="18">
         <f>SUM(G23:H29)</f>
-        <v>613</v>
-      </c>
-      <c r="H30" s="39"/>
-      <c r="I30" s="44">
+        <v>600</v>
+      </c>
+      <c r="H30" s="19"/>
+      <c r="I30" s="24">
         <f>G30/E30</f>
-        <v>0.94307692307692303</v>
-      </c>
-      <c r="J30" s="45"/>
-      <c r="K30" s="38" t="str">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="J30" s="25"/>
+      <c r="K30" s="18" t="str">
         <f>LOOKUP(I30*100,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
         <v>A+</v>
       </c>
-      <c r="L30" s="39"/>
-      <c r="M30" s="38" t="str">
+      <c r="L30" s="19"/>
+      <c r="M30" s="18" t="str">
         <f t="shared" ref="M30" si="2">IF(I30&lt;0.33,"FAIL","PASS")</f>
         <v>PASS</v>
       </c>
-      <c r="N30" s="47"/>
-      <c r="O30" s="39"/>
+      <c r="N30" s="23"/>
+      <c r="O30" s="19"/>
       <c r="P30" s="10"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="9"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -1741,126 +2165,160 @@
       <c r="O31" s="1"/>
       <c r="P31" s="10"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:16" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B32" s="9"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
+      <c r="C32" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="51">
+        <v>5</v>
+      </c>
+      <c r="G32" s="49" t="str">
+        <f>REPT("⭐",F32)</f>
+        <v>⭐⭐⭐⭐⭐</v>
+      </c>
+      <c r="H32" s="49"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
+      <c r="L32" s="49"/>
+      <c r="M32" s="49"/>
+      <c r="N32" s="49"/>
+      <c r="O32" s="50"/>
       <c r="P32" s="10"/>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="9"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
+      <c r="C33" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="57"/>
+      <c r="L33" s="57"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="57"/>
+      <c r="O33" s="58"/>
       <c r="P33" s="10"/>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B34" s="9"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
+      <c r="C34" s="54" t="str">
+        <f>REPT("⭐",1)</f>
+        <v>⭐</v>
+      </c>
+      <c r="D34" s="55"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="55"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="K34" s="62"/>
+      <c r="L34" s="62"/>
+      <c r="M34" s="62"/>
+      <c r="N34" s="62"/>
+      <c r="O34" s="63"/>
       <c r="P34" s="10"/>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="9"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
+      <c r="C35" s="54" t="str">
+        <f>REPT("⭐",2)</f>
+        <v>⭐⭐</v>
+      </c>
+      <c r="D35" s="55"/>
+      <c r="E35" s="55"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="55"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="K35" s="62"/>
+      <c r="L35" s="62"/>
+      <c r="M35" s="62"/>
+      <c r="N35" s="62"/>
+      <c r="O35" s="63"/>
       <c r="P35" s="10"/>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B36" s="9"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
+      <c r="C36" s="54" t="str">
+        <f>REPT("⭐",3)</f>
+        <v>⭐⭐⭐</v>
+      </c>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="61" t="s">
+        <v>15</v>
+      </c>
+      <c r="K36" s="62"/>
+      <c r="L36" s="62"/>
+      <c r="M36" s="62"/>
+      <c r="N36" s="62"/>
+      <c r="O36" s="63"/>
       <c r="P36" s="10"/>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="9"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
+      <c r="C37" s="54" t="str">
+        <f>REPT("⭐",4)</f>
+        <v>⭐⭐⭐⭐</v>
+      </c>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="K37" s="62"/>
+      <c r="L37" s="62"/>
+      <c r="M37" s="62"/>
+      <c r="N37" s="62"/>
+      <c r="O37" s="63"/>
       <c r="P37" s="10"/>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B38" s="9"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
+      <c r="C38" s="54" t="str">
+        <f>REPT("⭐",5)</f>
+        <v>⭐⭐⭐⭐⭐</v>
+      </c>
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="K38" s="62"/>
+      <c r="L38" s="62"/>
+      <c r="M38" s="62"/>
+      <c r="N38" s="62"/>
+      <c r="O38" s="63"/>
       <c r="P38" s="10"/>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="9"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -1877,16 +2335,20 @@
       <c r="O39" s="1"/>
       <c r="P39" s="10"/>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="9"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
+      <c r="C40" s="64" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="65"/>
+      <c r="E40" s="65"/>
+      <c r="F40" s="65"/>
+      <c r="G40" s="65"/>
+      <c r="H40" s="24">
+        <v>0.9</v>
+      </c>
+      <c r="I40" s="67"/>
+      <c r="J40" s="25"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -1911,7 +2373,7 @@
       <c r="O41" s="1"/>
       <c r="P41" s="10"/>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="9"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -1928,21 +2390,29 @@
       <c r="O42" s="1"/>
       <c r="P42" s="10"/>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="9"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
+      <c r="C43" s="70" t="s">
+        <v>82</v>
+      </c>
+      <c r="D43" s="69"/>
+      <c r="E43" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F43" s="44"/>
+      <c r="G43" s="45"/>
       <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
+      <c r="I43" s="70" t="s">
+        <v>83</v>
+      </c>
+      <c r="J43" s="71"/>
+      <c r="K43" s="71"/>
+      <c r="L43" s="71"/>
+      <c r="M43" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="N43" s="60"/>
+      <c r="O43" s="68"/>
       <c r="P43" s="10"/>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.25">
@@ -2049,9 +2519,9 @@
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B50" s="9"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -2099,7 +2569,90 @@
       <c r="P52" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="79">
+  <mergeCells count="98">
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="C36:I36"/>
+    <mergeCell ref="C37:I37"/>
+    <mergeCell ref="C38:I38"/>
+    <mergeCell ref="J34:O34"/>
+    <mergeCell ref="J35:O35"/>
+    <mergeCell ref="J36:O36"/>
+    <mergeCell ref="J37:O37"/>
+    <mergeCell ref="J38:O38"/>
+    <mergeCell ref="G32:O32"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C33:O33"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C3:O3"/>
+    <mergeCell ref="D4:N4"/>
+    <mergeCell ref="E5:M5"/>
+    <mergeCell ref="D6:N6"/>
+    <mergeCell ref="C10:O10"/>
+    <mergeCell ref="C11:O11"/>
+    <mergeCell ref="C12:O12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="C20:O20"/>
+    <mergeCell ref="C21:O21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G29:H29"/>
     <mergeCell ref="K30:L30"/>
     <mergeCell ref="M22:O22"/>
     <mergeCell ref="M23:O23"/>
@@ -2115,76 +2668,18 @@
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="K28:L28"/>
     <mergeCell ref="K29:L29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C20:O20"/>
-    <mergeCell ref="C21:O21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="C10:O10"/>
-    <mergeCell ref="C11:O11"/>
-    <mergeCell ref="C12:O12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C3:O3"/>
-    <mergeCell ref="D4:N4"/>
-    <mergeCell ref="E5:M5"/>
-    <mergeCell ref="D6:N6"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F32" xr:uid="{25D160CD-41E1-400F-8FC6-9677D68E1D32}">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D6" r:id="rId1" xr:uid="{02A21183-A0C8-4D99-B719-FFA62D55BA23}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="73" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
+  <drawing r:id="rId3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -2206,10 +2701,10 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -2224,49 +2719,49 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" t="s">
         <v>56</v>
       </c>
-      <c r="C1" t="s">
+      <c r="K1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" t="s">
+      <c r="L1" t="s">
         <v>58</v>
-      </c>
-      <c r="E1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L1" t="s">
-        <v>70</v>
       </c>
       <c r="M1" t="s">
         <v>0</v>
       </c>
       <c r="N1" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="O1" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -2274,10 +2769,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" t="s">
+        <v>100</v>
       </c>
       <c r="F2">
         <v>5</v>
+      </c>
+      <c r="G2" s="72" t="s">
+        <v>87</v>
+      </c>
+      <c r="H2" s="66">
+        <v>0.9</v>
       </c>
       <c r="I2">
         <v>97</v>
@@ -2306,10 +2816,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>88</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" t="s">
+        <v>100</v>
       </c>
       <c r="F3">
         <v>5</v>
+      </c>
+      <c r="G3" s="72" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3" s="66">
+        <v>0.9</v>
       </c>
       <c r="I3">
         <v>92</v>
@@ -2338,10 +2863,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>5</v>
+      </c>
+      <c r="H4" s="66">
+        <v>0.9</v>
       </c>
       <c r="I4">
         <v>92</v>
@@ -2370,10 +2898,23 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>92</v>
+      </c>
+      <c r="C5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>98</v>
       </c>
       <c r="F5">
         <v>5</v>
+      </c>
+      <c r="G5" s="72"/>
+      <c r="H5" s="66">
+        <v>0.9</v>
       </c>
       <c r="I5">
         <v>98</v>
@@ -2402,10 +2943,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>116</v>
+      </c>
+      <c r="C6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" t="s">
+        <v>100</v>
       </c>
       <c r="F6">
         <v>5</v>
+      </c>
+      <c r="G6" s="72" t="s">
+        <v>119</v>
+      </c>
+      <c r="H6" s="66">
+        <v>0.9</v>
       </c>
       <c r="I6">
         <v>98</v>
@@ -2434,10 +2990,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>125</v>
+      </c>
+      <c r="C7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7" t="s">
+        <v>114</v>
       </c>
       <c r="F7">
         <v>5</v>
+      </c>
+      <c r="G7" s="72" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" s="66">
+        <v>0.9</v>
       </c>
       <c r="I7">
         <v>88</v>
@@ -2466,10 +3037,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>120</v>
+      </c>
+      <c r="C8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" t="s">
+        <v>123</v>
       </c>
       <c r="F8">
         <v>5</v>
+      </c>
+      <c r="G8" s="79" t="s">
+        <v>124</v>
+      </c>
+      <c r="H8" s="66">
+        <v>0.9</v>
       </c>
       <c r="I8">
         <v>96</v>
@@ -2498,10 +3084,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" t="s">
+        <v>109</v>
       </c>
       <c r="F9">
         <v>5</v>
+      </c>
+      <c r="G9" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="H9" s="66">
+        <v>0.9</v>
       </c>
       <c r="I9">
         <v>87</v>
@@ -2529,11 +3130,26 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>9</v>
+      <c r="B10" s="78" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="78" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" t="s">
+        <v>105</v>
       </c>
       <c r="F10">
         <v>5</v>
+      </c>
+      <c r="G10" s="72" t="s">
+        <v>106</v>
+      </c>
+      <c r="H10" s="66">
+        <v>0.9</v>
       </c>
       <c r="I10">
         <v>90</v>
@@ -2562,19 +3178,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="F11">
         <v>5</v>
+      </c>
+      <c r="G11" s="72" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="66">
+        <v>0.9</v>
       </c>
       <c r="I11">
         <v>87</v>
@@ -2603,10 +3225,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>5</v>
+      </c>
+      <c r="H12" s="66">
+        <v>0.9</v>
       </c>
       <c r="I12">
         <v>80</v>
@@ -2635,10 +3260,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>111</v>
+      </c>
+      <c r="C13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E13" t="s">
+        <v>114</v>
       </c>
       <c r="F13">
         <v>5</v>
+      </c>
+      <c r="G13" s="72" t="s">
+        <v>115</v>
+      </c>
+      <c r="H13" s="66">
+        <v>0.9</v>
       </c>
       <c r="I13">
         <v>82</v>
@@ -2667,10 +3307,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F14">
         <v>5</v>
+      </c>
+      <c r="H14" s="66">
+        <v>0.9</v>
       </c>
       <c r="I14">
         <v>85</v>
@@ -2699,10 +3342,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>5</v>
+      </c>
+      <c r="H15" s="66">
+        <v>0.9</v>
       </c>
       <c r="I15">
         <v>80</v>
@@ -2731,10 +3377,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F16">
         <v>5</v>
+      </c>
+      <c r="H16" s="66">
+        <v>0.9</v>
       </c>
       <c r="I16">
         <v>80</v>
@@ -2763,10 +3412,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F17">
         <v>5</v>
+      </c>
+      <c r="H17" s="66">
+        <v>0.9</v>
       </c>
       <c r="I17">
         <v>80</v>
@@ -2795,10 +3447,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F18">
         <v>5</v>
+      </c>
+      <c r="H18" s="66">
+        <v>0.9</v>
       </c>
       <c r="I18">
         <v>80</v>
@@ -2827,10 +3482,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F19">
         <v>5</v>
+      </c>
+      <c r="H19" s="66">
+        <v>0.9</v>
       </c>
       <c r="I19">
         <v>80</v>
@@ -2859,10 +3517,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F20">
         <v>5</v>
+      </c>
+      <c r="H20" s="66">
+        <v>0.9</v>
       </c>
       <c r="I20">
         <v>85</v>
@@ -2891,10 +3552,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F21">
         <v>5</v>
+      </c>
+      <c r="H21" s="66">
+        <v>0.9</v>
       </c>
       <c r="I21">
         <v>80</v>
@@ -2941,10 +3605,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C2" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="17"/>
+      <c r="C2" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="42"/>
       <c r="E2" s="4"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
@@ -2952,7 +3616,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E3" s="4"/>
     </row>
@@ -2961,7 +3625,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E4" s="4"/>
     </row>
@@ -2970,7 +3634,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E5" s="4"/>
     </row>
@@ -2979,7 +3643,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E6" s="4"/>
     </row>
@@ -2988,242 +3652,242 @@
         <v>5</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E7" s="4"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E11" s="5">
         <v>0</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E12" s="5">
         <v>33</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K12" s="5">
         <v>17</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E13" s="5">
         <v>41</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="K13" s="5">
         <v>21</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E14" s="5">
         <v>51</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="K14" s="5">
         <v>26</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E15" s="5">
         <v>61</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="K15" s="5">
         <v>31</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E16" s="5">
         <v>71</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="K16" s="5">
         <v>36</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E17" s="5">
         <v>81</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="K17" s="5">
         <v>41</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E18" s="5">
         <v>91</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="K18" s="5">
         <v>45</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/marksheet.xlsx
+++ b/marksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atosh\OneDrive\Desktop\Study-Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9BCEE8-4BBB-4D76-8009-D434DB5DA315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66D2390-2F2A-4A9D-B419-82D9C36000A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReportCard" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="139">
   <si>
     <t>BGS</t>
   </si>
@@ -52,12 +52,6 @@
     <t>Sathi Sharma</t>
   </si>
   <si>
-    <t>Rabbi Islam</t>
-  </si>
-  <si>
-    <t>Mijan Islam</t>
-  </si>
-  <si>
     <t>Farjana Akther</t>
   </si>
   <si>
@@ -73,12 +67,6 @@
     <t>Chondo Roy</t>
   </si>
   <si>
-    <t>Nahim Islam</t>
-  </si>
-  <si>
-    <t>Najmul Islam</t>
-  </si>
-  <si>
     <t>Star Rating</t>
   </si>
   <si>
@@ -428,6 +416,48 @@
   </si>
   <si>
     <t>01726759389</t>
+  </si>
+  <si>
+    <t>Ferazul Islam</t>
+  </si>
+  <si>
+    <t>Rina Parvin</t>
+  </si>
+  <si>
+    <t>Kanial Khata</t>
+  </si>
+  <si>
+    <t>01790524726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Md Mijan </t>
+  </si>
+  <si>
+    <t>Md Jakirul</t>
+  </si>
+  <si>
+    <t>Khadija Begum</t>
+  </si>
+  <si>
+    <t>Md Nazmul Huda</t>
+  </si>
+  <si>
+    <t>Md. Habibur Rahman</t>
+  </si>
+  <si>
+    <t>Narzina Begum</t>
+  </si>
+  <si>
+    <t>Md Nayem Islam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Md Fazle Rabbi </t>
+  </si>
+  <si>
+    <t>Md Hamidul Haque</t>
+  </si>
+  <si>
+    <t>Simu Khatun</t>
   </si>
 </sst>
 </file>
@@ -792,168 +822,168 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1490,39 +1520,39 @@
     </row>
     <row r="3" spans="2:16" ht="33.75" x14ac:dyDescent="0.25">
       <c r="B3" s="9"/>
-      <c r="C3" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
+      <c r="C3" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
       <c r="P3" s="10"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B4" s="9"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
+      <c r="D4" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="56"/>
       <c r="O4" s="1"/>
       <c r="P4" s="10"/>
     </row>
@@ -1530,17 +1560,17 @@
       <c r="B5" s="9"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="35" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
+      <c r="E5" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="10"/>
@@ -1548,19 +1578,19 @@
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="9"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
+      <c r="D6" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
       <c r="O6" s="2"/>
       <c r="P6" s="10"/>
     </row>
@@ -1570,11 +1600,11 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" s="9"/>
-      <c r="C8" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
+      <c r="C8" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1582,11 +1612,11 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
-      <c r="M8" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
+      <c r="M8" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="N8" s="51"/>
+      <c r="O8" s="51"/>
       <c r="P8" s="10"/>
     </row>
     <row r="9" spans="2:16" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1608,143 +1638,143 @@
     </row>
     <row r="10" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="9"/>
-      <c r="C10" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="75"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
-      <c r="J10" s="75"/>
-      <c r="K10" s="75"/>
-      <c r="L10" s="75"/>
-      <c r="M10" s="75"/>
-      <c r="N10" s="75"/>
-      <c r="O10" s="75"/>
+      <c r="C10" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="60"/>
+      <c r="N10" s="60"/>
+      <c r="O10" s="60"/>
       <c r="P10" s="10"/>
     </row>
     <row r="11" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="9"/>
-      <c r="C11" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
-      <c r="J11" s="75"/>
-      <c r="K11" s="75"/>
-      <c r="L11" s="75"/>
-      <c r="M11" s="75"/>
-      <c r="N11" s="75"/>
-      <c r="O11" s="75"/>
+      <c r="C11" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="60"/>
+      <c r="L11" s="60"/>
+      <c r="M11" s="60"/>
+      <c r="N11" s="60"/>
+      <c r="O11" s="60"/>
       <c r="P11" s="10"/>
     </row>
     <row r="12" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B12" s="9"/>
-      <c r="C12" s="76" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="75"/>
-      <c r="E12" s="75"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75"/>
-      <c r="J12" s="75"/>
-      <c r="K12" s="75"/>
-      <c r="L12" s="75"/>
-      <c r="M12" s="75"/>
-      <c r="N12" s="75"/>
-      <c r="O12" s="75"/>
+      <c r="C12" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="60"/>
+      <c r="L12" s="60"/>
+      <c r="M12" s="60"/>
+      <c r="N12" s="60"/>
+      <c r="O12" s="60"/>
       <c r="P12" s="10"/>
     </row>
     <row r="13" spans="2:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="9"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="77"/>
-      <c r="K13" s="77"/>
-      <c r="L13" s="77"/>
-      <c r="M13" s="77"/>
-      <c r="N13" s="77"/>
-      <c r="O13" s="77"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
       <c r="P13" s="10"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B14" s="9"/>
-      <c r="C14" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="31"/>
-      <c r="E14" s="33">
-        <v>10</v>
-      </c>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
+      <c r="C14" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="62"/>
+      <c r="E14" s="66">
+        <v>3</v>
+      </c>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
-      <c r="K14" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="L14" s="31"/>
-      <c r="M14" s="73">
+      <c r="K14" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="L14" s="62"/>
+      <c r="M14" s="63">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!K14,DataBase!$A$1:$O$1,0),0)</f>
         <v>5</v>
       </c>
-      <c r="N14" s="73"/>
-      <c r="O14" s="73"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="63"/>
       <c r="P14" s="10"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B15" s="9"/>
-      <c r="C15" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="31"/>
-      <c r="E15" s="34" t="str">
+      <c r="C15" s="62" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="62"/>
+      <c r="E15" s="64" t="str">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!C15,DataBase!$A$1:$O$1,0),0)</f>
-        <v>Nuri Akter</v>
-      </c>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
+        <v>Imran Islam</v>
+      </c>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
-      <c r="K15" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="L15" s="31"/>
-      <c r="M15" s="34" t="str">
+      <c r="K15" s="62" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="62"/>
+      <c r="M15" s="64" t="str">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!K15,DataBase!$A$1:$O$1,0),0)</f>
-        <v>01346468836</v>
-      </c>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
+        <v>01790524726</v>
+      </c>
+      <c r="N15" s="64"/>
+      <c r="O15" s="64"/>
       <c r="P15" s="10"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B16" s="9"/>
-      <c r="C16" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="34" t="str">
+      <c r="C16" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="62"/>
+      <c r="E16" s="64" t="str">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!C16,DataBase!$A$1:$O$1,0),0)</f>
-        <v xml:space="preserve">Nur Mohammad </v>
-      </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
+        <v>Ferazul Islam</v>
+      </c>
+      <c r="F16" s="64"/>
+      <c r="G16" s="64"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1757,16 +1787,16 @@
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B17" s="9"/>
-      <c r="C17" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="34" t="str">
+      <c r="C17" s="65" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="65"/>
+      <c r="E17" s="64" t="str">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!C17,DataBase!$A$1:$O$1,0),0)</f>
-        <v>Mrs. Nasima Begum</v>
-      </c>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
+        <v>Rina Parvin</v>
+      </c>
+      <c r="F17" s="64"/>
+      <c r="G17" s="64"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1779,16 +1809,16 @@
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B18" s="9"/>
-      <c r="C18" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="32"/>
-      <c r="E18" s="34" t="str">
+      <c r="C18" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="65"/>
+      <c r="E18" s="64" t="str">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!C18,DataBase!$A$1:$O$1,0),0)</f>
-        <v>Kanial Khata Munsipara</v>
-      </c>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
+        <v>Kanial Khata</v>
+      </c>
+      <c r="F18" s="64"/>
+      <c r="G18" s="64"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -1818,334 +1848,334 @@
     </row>
     <row r="20" spans="2:16" ht="23.25" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B20" s="9"/>
-      <c r="C20" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
+      <c r="C20" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="67"/>
+      <c r="K20" s="67"/>
+      <c r="L20" s="67"/>
+      <c r="M20" s="67"/>
+      <c r="N20" s="67"/>
+      <c r="O20" s="67"/>
       <c r="P20" s="10"/>
     </row>
     <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="9"/>
-      <c r="C21" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="47"/>
-      <c r="O21" s="48"/>
+      <c r="C21" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="69"/>
+      <c r="K21" s="69"/>
+      <c r="L21" s="69"/>
+      <c r="M21" s="69"/>
+      <c r="N21" s="69"/>
+      <c r="O21" s="70"/>
       <c r="P21" s="10"/>
     </row>
     <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="9"/>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="71"/>
+      <c r="E22" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="75"/>
+      <c r="G22" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="H22" s="75"/>
+      <c r="I22" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="30"/>
-      <c r="E22" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="F22" s="22"/>
-      <c r="G22" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H22" s="22"/>
-      <c r="I22" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="J22" s="22"/>
-      <c r="K22" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="L22" s="22"/>
-      <c r="M22" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="N22" s="21"/>
-      <c r="O22" s="22"/>
+      <c r="J22" s="75"/>
+      <c r="K22" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="L22" s="75"/>
+      <c r="M22" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="N22" s="77"/>
+      <c r="O22" s="75"/>
       <c r="P22" s="10"/>
     </row>
     <row r="23" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="9"/>
-      <c r="C23" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="27"/>
-      <c r="E23" s="18">
+      <c r="C23" s="72" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="73"/>
+      <c r="E23" s="32">
         <v>100</v>
       </c>
-      <c r="F23" s="19"/>
-      <c r="G23" s="18">
+      <c r="F23" s="76"/>
+      <c r="G23" s="32">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C23,DataBase!$A$1:$O$1,0),0)</f>
-        <v>87</v>
-      </c>
-      <c r="H23" s="19"/>
-      <c r="I23" s="24">
+        <v>92</v>
+      </c>
+      <c r="H23" s="76"/>
+      <c r="I23" s="29">
         <f>G23/E23</f>
-        <v>0.87</v>
-      </c>
-      <c r="J23" s="25"/>
-      <c r="K23" s="18" t="str">
+        <v>0.92</v>
+      </c>
+      <c r="J23" s="31"/>
+      <c r="K23" s="32" t="str">
         <f>LOOKUP(G23,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
-        <v>A</v>
-      </c>
-      <c r="L23" s="19"/>
-      <c r="M23" s="18" t="str">
+        <v>A+</v>
+      </c>
+      <c r="L23" s="76"/>
+      <c r="M23" s="32" t="str">
         <f>IF(I23&lt;0.33,"FAIL","PASS")</f>
         <v>PASS</v>
       </c>
-      <c r="N23" s="23"/>
-      <c r="O23" s="19"/>
+      <c r="N23" s="78"/>
+      <c r="O23" s="76"/>
       <c r="P23" s="10"/>
     </row>
     <row r="24" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="9"/>
-      <c r="C24" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="27"/>
-      <c r="E24" s="18">
+      <c r="C24" s="72" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="73"/>
+      <c r="E24" s="32">
         <v>100</v>
       </c>
-      <c r="F24" s="19"/>
-      <c r="G24" s="18">
+      <c r="F24" s="76"/>
+      <c r="G24" s="32">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C24,DataBase!$A$1:$O$1,0),0)</f>
-        <v>98</v>
-      </c>
-      <c r="H24" s="19"/>
-      <c r="I24" s="24">
+        <v>97</v>
+      </c>
+      <c r="H24" s="76"/>
+      <c r="I24" s="29">
         <f t="shared" ref="I24:I29" si="0">G24/E24</f>
-        <v>0.98</v>
-      </c>
-      <c r="J24" s="25"/>
-      <c r="K24" s="18" t="str">
+        <v>0.97</v>
+      </c>
+      <c r="J24" s="31"/>
+      <c r="K24" s="32" t="str">
         <f>LOOKUP(G24,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
         <v>A+</v>
       </c>
-      <c r="L24" s="19"/>
-      <c r="M24" s="18" t="str">
+      <c r="L24" s="76"/>
+      <c r="M24" s="32" t="str">
         <f t="shared" ref="M24:M29" si="1">IF(I24&lt;0.33,"FAIL","PASS")</f>
         <v>PASS</v>
       </c>
-      <c r="N24" s="23"/>
-      <c r="O24" s="19"/>
+      <c r="N24" s="78"/>
+      <c r="O24" s="76"/>
       <c r="P24" s="10"/>
     </row>
     <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="9"/>
-      <c r="C25" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="27"/>
-      <c r="E25" s="18">
+      <c r="C25" s="72" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="73"/>
+      <c r="E25" s="32">
         <v>100</v>
       </c>
-      <c r="F25" s="19"/>
-      <c r="G25" s="18">
+      <c r="F25" s="76"/>
+      <c r="G25" s="32">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C25,DataBase!$A$1:$O$1,0),0)</f>
+        <v>98</v>
+      </c>
+      <c r="H25" s="76"/>
+      <c r="I25" s="29">
+        <f t="shared" si="0"/>
+        <v>0.98</v>
+      </c>
+      <c r="J25" s="31"/>
+      <c r="K25" s="32" t="str">
+        <f>LOOKUP(G25,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
+        <v>A+</v>
+      </c>
+      <c r="L25" s="76"/>
+      <c r="M25" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+      <c r="N25" s="78"/>
+      <c r="O25" s="76"/>
+      <c r="P25" s="10"/>
+    </row>
+    <row r="26" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="9"/>
+      <c r="C26" s="72" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="73"/>
+      <c r="E26" s="32">
+        <v>100</v>
+      </c>
+      <c r="F26" s="76"/>
+      <c r="G26" s="32">
+        <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C26,DataBase!$A$1:$O$1,0),0)</f>
+        <v>85</v>
+      </c>
+      <c r="H26" s="76"/>
+      <c r="I26" s="29">
+        <f t="shared" si="0"/>
+        <v>0.85</v>
+      </c>
+      <c r="J26" s="31"/>
+      <c r="K26" s="32" t="str">
+        <f>LOOKUP(G26,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
+        <v>A</v>
+      </c>
+      <c r="L26" s="76"/>
+      <c r="M26" s="32" t="str">
+        <f>IF(I26&lt;0.33,"FAIL","PASS")</f>
+        <v>PASS</v>
+      </c>
+      <c r="N26" s="78"/>
+      <c r="O26" s="76"/>
+      <c r="P26" s="10"/>
+    </row>
+    <row r="27" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="9"/>
+      <c r="C27" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="D27" s="73"/>
+      <c r="E27" s="32">
+        <v>100</v>
+      </c>
+      <c r="F27" s="76"/>
+      <c r="G27" s="32">
+        <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C27,DataBase!$A$1:$O$1,0),0)</f>
+        <v>94</v>
+      </c>
+      <c r="H27" s="76"/>
+      <c r="I27" s="29">
+        <f t="shared" si="0"/>
+        <v>0.94</v>
+      </c>
+      <c r="J27" s="31"/>
+      <c r="K27" s="32" t="str">
+        <f>LOOKUP(G27,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
+        <v>A+</v>
+      </c>
+      <c r="L27" s="76"/>
+      <c r="M27" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+      <c r="N27" s="78"/>
+      <c r="O27" s="76"/>
+      <c r="P27" s="10"/>
+    </row>
+    <row r="28" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="9"/>
+      <c r="C28" s="72" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="73"/>
+      <c r="E28" s="32">
+        <v>100</v>
+      </c>
+      <c r="F28" s="76"/>
+      <c r="G28" s="32">
+        <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C28,DataBase!$A$1:$O$1,0),0)</f>
         <v>95</v>
       </c>
-      <c r="H25" s="19"/>
-      <c r="I25" s="24">
+      <c r="H28" s="76"/>
+      <c r="I28" s="29">
         <f t="shared" si="0"/>
         <v>0.95</v>
       </c>
-      <c r="J25" s="25"/>
-      <c r="K25" s="18" t="str">
-        <f>LOOKUP(G25,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
+      <c r="J28" s="31"/>
+      <c r="K28" s="32" t="str">
+        <f>LOOKUP(G28,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
         <v>A+</v>
       </c>
-      <c r="L25" s="19"/>
-      <c r="M25" s="18" t="str">
+      <c r="L28" s="76"/>
+      <c r="M28" s="32" t="str">
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="N25" s="23"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="10"/>
-    </row>
-    <row r="26" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="9"/>
-      <c r="C26" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="18">
-        <v>100</v>
-      </c>
-      <c r="F26" s="19"/>
-      <c r="G26" s="18">
-        <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C26,DataBase!$A$1:$O$1,0),0)</f>
-        <v>92</v>
-      </c>
-      <c r="H26" s="19"/>
-      <c r="I26" s="24">
+      <c r="N28" s="78"/>
+      <c r="O28" s="76"/>
+      <c r="P28" s="10"/>
+    </row>
+    <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="9"/>
+      <c r="C29" s="72" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="73"/>
+      <c r="E29" s="32">
+        <v>50</v>
+      </c>
+      <c r="F29" s="76"/>
+      <c r="G29" s="32">
+        <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C29,DataBase!$A$1:$O$1,0),0)</f>
+        <v>46</v>
+      </c>
+      <c r="H29" s="76"/>
+      <c r="I29" s="29">
         <f t="shared" si="0"/>
         <v>0.92</v>
       </c>
-      <c r="J26" s="25"/>
-      <c r="K26" s="18" t="str">
-        <f>LOOKUP(G26,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
+      <c r="J29" s="31"/>
+      <c r="K29" s="32" t="str">
+        <f>LOOKUP(G29,Rating!$K$11:$K$18,Rating!$L$11:$L$18)</f>
         <v>A+</v>
       </c>
-      <c r="L26" s="19"/>
-      <c r="M26" s="18" t="str">
-        <f>IF(I26&lt;0.33,"FAIL","PASS")</f>
-        <v>PASS</v>
-      </c>
-      <c r="N26" s="23"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="10"/>
-    </row>
-    <row r="27" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="9"/>
-      <c r="C27" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="D27" s="27"/>
-      <c r="E27" s="18">
-        <v>100</v>
-      </c>
-      <c r="F27" s="19"/>
-      <c r="G27" s="18">
-        <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C27,DataBase!$A$1:$O$1,0),0)</f>
-        <v>98</v>
-      </c>
-      <c r="H27" s="19"/>
-      <c r="I27" s="24">
-        <f t="shared" si="0"/>
-        <v>0.98</v>
-      </c>
-      <c r="J27" s="25"/>
-      <c r="K27" s="18" t="str">
-        <f>LOOKUP(G27,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
-        <v>A+</v>
-      </c>
-      <c r="L27" s="19"/>
-      <c r="M27" s="18" t="str">
+      <c r="L29" s="76"/>
+      <c r="M29" s="32" t="str">
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="N27" s="23"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="10"/>
-    </row>
-    <row r="28" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="9"/>
-      <c r="C28" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" s="27"/>
-      <c r="E28" s="18">
-        <v>100</v>
-      </c>
-      <c r="F28" s="19"/>
-      <c r="G28" s="18">
-        <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C28,DataBase!$A$1:$O$1,0),0)</f>
-        <v>85</v>
-      </c>
-      <c r="H28" s="19"/>
-      <c r="I28" s="24">
-        <f t="shared" si="0"/>
-        <v>0.85</v>
-      </c>
-      <c r="J28" s="25"/>
-      <c r="K28" s="18" t="str">
-        <f>LOOKUP(G28,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
-        <v>A</v>
-      </c>
-      <c r="L28" s="19"/>
-      <c r="M28" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>PASS</v>
-      </c>
-      <c r="N28" s="23"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="10"/>
-    </row>
-    <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="9"/>
-      <c r="C29" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="27"/>
-      <c r="E29" s="18">
-        <v>50</v>
-      </c>
-      <c r="F29" s="19"/>
-      <c r="G29" s="18">
-        <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C29,DataBase!$A$1:$O$1,0),0)</f>
-        <v>45</v>
-      </c>
-      <c r="H29" s="19"/>
-      <c r="I29" s="24">
-        <f t="shared" si="0"/>
-        <v>0.9</v>
-      </c>
-      <c r="J29" s="25"/>
-      <c r="K29" s="18" t="str">
-        <f>LOOKUP(G29,Rating!$K$11:$K$18,Rating!$L$11:$L$18)</f>
-        <v>A+</v>
-      </c>
-      <c r="L29" s="19"/>
-      <c r="M29" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>PASS</v>
-      </c>
-      <c r="N29" s="23"/>
-      <c r="O29" s="19"/>
+      <c r="N29" s="78"/>
+      <c r="O29" s="76"/>
       <c r="P29" s="10"/>
     </row>
     <row r="30" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="9"/>
-      <c r="C30" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="18">
+      <c r="C30" s="72" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="73"/>
+      <c r="E30" s="32">
         <f>SUM(E23:F29)</f>
         <v>650</v>
       </c>
-      <c r="F30" s="19"/>
-      <c r="G30" s="18">
+      <c r="F30" s="76"/>
+      <c r="G30" s="32">
         <f>SUM(G23:H29)</f>
-        <v>600</v>
-      </c>
-      <c r="H30" s="19"/>
-      <c r="I30" s="24">
+        <v>607</v>
+      </c>
+      <c r="H30" s="76"/>
+      <c r="I30" s="29">
         <f>G30/E30</f>
-        <v>0.92307692307692313</v>
-      </c>
-      <c r="J30" s="25"/>
-      <c r="K30" s="18" t="str">
+        <v>0.93384615384615388</v>
+      </c>
+      <c r="J30" s="31"/>
+      <c r="K30" s="32" t="str">
         <f>LOOKUP(I30*100,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
         <v>A+</v>
       </c>
-      <c r="L30" s="19"/>
-      <c r="M30" s="18" t="str">
+      <c r="L30" s="76"/>
+      <c r="M30" s="32" t="str">
         <f t="shared" ref="M30" si="2">IF(I30&lt;0.33,"FAIL","PASS")</f>
         <v>PASS</v>
       </c>
-      <c r="N30" s="23"/>
-      <c r="O30" s="19"/>
+      <c r="N30" s="78"/>
+      <c r="O30" s="76"/>
       <c r="P30" s="10"/>
     </row>
     <row r="31" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2167,155 +2197,155 @@
     </row>
     <row r="32" spans="2:16" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B32" s="9"/>
-      <c r="C32" s="52" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="51">
+      <c r="C32" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="18">
         <v>5</v>
       </c>
-      <c r="G32" s="49" t="str">
+      <c r="G32" s="44" t="str">
         <f>REPT("⭐",F32)</f>
         <v>⭐⭐⭐⭐⭐</v>
       </c>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
-      <c r="L32" s="49"/>
-      <c r="M32" s="49"/>
-      <c r="N32" s="49"/>
-      <c r="O32" s="50"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44"/>
+      <c r="L32" s="44"/>
+      <c r="M32" s="44"/>
+      <c r="N32" s="44"/>
+      <c r="O32" s="45"/>
       <c r="P32" s="10"/>
     </row>
     <row r="33" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="9"/>
-      <c r="C33" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="D33" s="57"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="57"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="57"/>
-      <c r="K33" s="57"/>
-      <c r="L33" s="57"/>
-      <c r="M33" s="57"/>
-      <c r="N33" s="57"/>
-      <c r="O33" s="58"/>
+      <c r="C33" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="49"/>
+      <c r="J33" s="49"/>
+      <c r="K33" s="49"/>
+      <c r="L33" s="49"/>
+      <c r="M33" s="49"/>
+      <c r="N33" s="49"/>
+      <c r="O33" s="50"/>
       <c r="P33" s="10"/>
     </row>
     <row r="34" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B34" s="9"/>
-      <c r="C34" s="54" t="str">
+      <c r="C34" s="38" t="str">
         <f>REPT("⭐",1)</f>
         <v>⭐</v>
       </c>
-      <c r="D34" s="55"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="55"/>
-      <c r="H34" s="55"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="61" t="s">
-        <v>13</v>
-      </c>
-      <c r="K34" s="62"/>
-      <c r="L34" s="62"/>
-      <c r="M34" s="62"/>
-      <c r="N34" s="62"/>
-      <c r="O34" s="63"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="K34" s="42"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="42"/>
+      <c r="N34" s="42"/>
+      <c r="O34" s="43"/>
       <c r="P34" s="10"/>
     </row>
     <row r="35" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="9"/>
-      <c r="C35" s="54" t="str">
+      <c r="C35" s="38" t="str">
         <f>REPT("⭐",2)</f>
         <v>⭐⭐</v>
       </c>
-      <c r="D35" s="55"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="55"/>
-      <c r="H35" s="55"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="K35" s="62"/>
-      <c r="L35" s="62"/>
-      <c r="M35" s="62"/>
-      <c r="N35" s="62"/>
-      <c r="O35" s="63"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K35" s="42"/>
+      <c r="L35" s="42"/>
+      <c r="M35" s="42"/>
+      <c r="N35" s="42"/>
+      <c r="O35" s="43"/>
       <c r="P35" s="10"/>
     </row>
     <row r="36" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B36" s="9"/>
-      <c r="C36" s="54" t="str">
+      <c r="C36" s="38" t="str">
         <f>REPT("⭐",3)</f>
         <v>⭐⭐⭐</v>
       </c>
-      <c r="D36" s="55"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="56"/>
-      <c r="J36" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="K36" s="62"/>
-      <c r="L36" s="62"/>
-      <c r="M36" s="62"/>
-      <c r="N36" s="62"/>
-      <c r="O36" s="63"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="40"/>
+      <c r="J36" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="43"/>
       <c r="P36" s="10"/>
     </row>
     <row r="37" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="9"/>
-      <c r="C37" s="54" t="str">
+      <c r="C37" s="38" t="str">
         <f>REPT("⭐",4)</f>
         <v>⭐⭐⭐⭐</v>
       </c>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="56"/>
-      <c r="J37" s="61" t="s">
-        <v>16</v>
-      </c>
-      <c r="K37" s="62"/>
-      <c r="L37" s="62"/>
-      <c r="M37" s="62"/>
-      <c r="N37" s="62"/>
-      <c r="O37" s="63"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="K37" s="42"/>
+      <c r="L37" s="42"/>
+      <c r="M37" s="42"/>
+      <c r="N37" s="42"/>
+      <c r="O37" s="43"/>
       <c r="P37" s="10"/>
     </row>
     <row r="38" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B38" s="9"/>
-      <c r="C38" s="54" t="str">
+      <c r="C38" s="38" t="str">
         <f>REPT("⭐",5)</f>
         <v>⭐⭐⭐⭐⭐</v>
       </c>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="56"/>
-      <c r="J38" s="61" t="s">
-        <v>79</v>
-      </c>
-      <c r="K38" s="62"/>
-      <c r="L38" s="62"/>
-      <c r="M38" s="62"/>
-      <c r="N38" s="62"/>
-      <c r="O38" s="63"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="40"/>
+      <c r="J38" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="K38" s="42"/>
+      <c r="L38" s="42"/>
+      <c r="M38" s="42"/>
+      <c r="N38" s="42"/>
+      <c r="O38" s="43"/>
       <c r="P38" s="10"/>
     </row>
     <row r="39" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2337,18 +2367,18 @@
     </row>
     <row r="40" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="9"/>
-      <c r="C40" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" s="65"/>
-      <c r="E40" s="65"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="65"/>
-      <c r="H40" s="24">
+      <c r="C40" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="29">
         <v>0.9</v>
       </c>
-      <c r="I40" s="67"/>
-      <c r="J40" s="25"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="31"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -2392,27 +2422,27 @@
     </row>
     <row r="43" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="9"/>
-      <c r="C43" s="70" t="s">
-        <v>82</v>
-      </c>
-      <c r="D43" s="69"/>
-      <c r="E43" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="F43" s="44"/>
-      <c r="G43" s="45"/>
+      <c r="C43" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="D43" s="36"/>
+      <c r="E43" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" s="33"/>
+      <c r="G43" s="34"/>
       <c r="H43" s="1"/>
-      <c r="I43" s="70" t="s">
-        <v>83</v>
-      </c>
-      <c r="J43" s="71"/>
-      <c r="K43" s="71"/>
-      <c r="L43" s="71"/>
-      <c r="M43" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="N43" s="60"/>
-      <c r="O43" s="68"/>
+      <c r="I43" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="J43" s="37"/>
+      <c r="K43" s="37"/>
+      <c r="L43" s="37"/>
+      <c r="M43" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="N43" s="26"/>
+      <c r="O43" s="20"/>
       <c r="P43" s="10"/>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.25">
@@ -2570,59 +2600,36 @@
     </row>
   </sheetData>
   <mergeCells count="98">
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="C35:I35"/>
-    <mergeCell ref="C36:I36"/>
-    <mergeCell ref="C37:I37"/>
-    <mergeCell ref="C38:I38"/>
-    <mergeCell ref="J34:O34"/>
-    <mergeCell ref="J35:O35"/>
-    <mergeCell ref="J36:O36"/>
-    <mergeCell ref="J37:O37"/>
-    <mergeCell ref="J38:O38"/>
-    <mergeCell ref="G32:O32"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C33:O33"/>
-    <mergeCell ref="C34:I34"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C3:O3"/>
-    <mergeCell ref="D4:N4"/>
-    <mergeCell ref="E5:M5"/>
-    <mergeCell ref="D6:N6"/>
-    <mergeCell ref="C10:O10"/>
-    <mergeCell ref="C11:O11"/>
-    <mergeCell ref="C12:O12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="C20:O20"/>
-    <mergeCell ref="C21:O21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G29:H29"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="E23:F23"/>
@@ -2638,36 +2645,59 @@
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="C29:D29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="M27:O27"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="C20:O20"/>
+    <mergeCell ref="C21:O21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="C3:O3"/>
+    <mergeCell ref="D4:N4"/>
+    <mergeCell ref="E5:M5"/>
+    <mergeCell ref="D6:N6"/>
+    <mergeCell ref="C10:O10"/>
+    <mergeCell ref="G32:O32"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C33:O33"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C11:O11"/>
+    <mergeCell ref="C12:O12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="C36:I36"/>
+    <mergeCell ref="C37:I37"/>
+    <mergeCell ref="C38:I38"/>
+    <mergeCell ref="J34:O34"/>
+    <mergeCell ref="J35:O35"/>
+    <mergeCell ref="J36:O36"/>
+    <mergeCell ref="J37:O37"/>
+    <mergeCell ref="J38:O38"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="I43:L43"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F32" xr:uid="{25D160CD-41E1-400F-8FC6-9677D68E1D32}">
@@ -2719,49 +2749,49 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>53</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>54</v>
-      </c>
-      <c r="I1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K1" t="s">
-        <v>57</v>
-      </c>
-      <c r="L1" t="s">
-        <v>58</v>
       </c>
       <c r="M1" t="s">
         <v>0</v>
       </c>
       <c r="N1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="O1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -2769,24 +2799,24 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F2">
         <v>5</v>
       </c>
-      <c r="G2" s="72" t="s">
-        <v>87</v>
-      </c>
-      <c r="H2" s="66">
+      <c r="G2" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" s="19">
         <v>0.9</v>
       </c>
       <c r="I2">
@@ -2816,24 +2846,24 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
-      <c r="G3" s="72" t="s">
-        <v>91</v>
-      </c>
-      <c r="H3" s="66">
+      <c r="G3" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="19">
         <v>0.9</v>
       </c>
       <c r="I3">
@@ -2865,10 +2895,22 @@
       <c r="B4" t="s">
         <v>1</v>
       </c>
+      <c r="C4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" t="s">
+        <v>127</v>
+      </c>
       <c r="F4">
         <v>5</v>
       </c>
-      <c r="H4" s="66">
+      <c r="G4" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="H4" s="19">
         <v>0.9</v>
       </c>
       <c r="I4">
@@ -2898,22 +2940,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" t="s">
         <v>94</v>
-      </c>
-      <c r="E5" t="s">
-        <v>98</v>
       </c>
       <c r="F5">
         <v>5</v>
       </c>
-      <c r="G5" s="72"/>
-      <c r="H5" s="66">
+      <c r="G5" s="21"/>
+      <c r="H5" s="19">
         <v>0.9</v>
       </c>
       <c r="I5">
@@ -2943,24 +2985,24 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F6">
         <v>5</v>
       </c>
-      <c r="G6" s="72" t="s">
-        <v>119</v>
-      </c>
-      <c r="H6" s="66">
+      <c r="G6" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="H6" s="19">
         <v>0.9</v>
       </c>
       <c r="I6">
@@ -2990,24 +3032,24 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
-      <c r="G7" s="72" t="s">
-        <v>128</v>
-      </c>
-      <c r="H7" s="66">
+      <c r="G7" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="H7" s="19">
         <v>0.9</v>
       </c>
       <c r="I7">
@@ -3037,24 +3079,24 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F8">
         <v>5</v>
       </c>
-      <c r="G8" s="79" t="s">
-        <v>124</v>
-      </c>
-      <c r="H8" s="66">
+      <c r="G8" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="H8" s="19">
         <v>0.9</v>
       </c>
       <c r="I8">
@@ -3087,21 +3129,21 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F9">
         <v>5</v>
       </c>
-      <c r="G9" s="72" t="s">
-        <v>110</v>
-      </c>
-      <c r="H9" s="66">
+      <c r="G9" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="H9" s="19">
         <v>0.9</v>
       </c>
       <c r="I9">
@@ -3130,25 +3172,25 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="78" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10" s="78" t="s">
-        <v>103</v>
+      <c r="B10" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F10">
         <v>5</v>
       </c>
-      <c r="G10" s="72" t="s">
-        <v>106</v>
-      </c>
-      <c r="H10" s="66">
+      <c r="G10" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="19">
         <v>0.9</v>
       </c>
       <c r="I10">
@@ -3178,24 +3220,24 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" t="s">
         <v>95</v>
-      </c>
-      <c r="C11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" t="s">
-        <v>99</v>
       </c>
       <c r="F11">
         <v>5</v>
       </c>
-      <c r="G11" s="72" t="s">
-        <v>101</v>
-      </c>
-      <c r="H11" s="66">
+      <c r="G11" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="H11" s="19">
         <v>0.9</v>
       </c>
       <c r="I11">
@@ -3225,12 +3267,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>136</v>
+      </c>
+      <c r="C12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12" t="s">
+        <v>94</v>
       </c>
       <c r="F12">
         <v>5</v>
       </c>
-      <c r="H12" s="66">
+      <c r="G12" s="21"/>
+      <c r="H12" s="19">
         <v>0.9</v>
       </c>
       <c r="I12">
@@ -3260,24 +3312,24 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F13">
         <v>5</v>
       </c>
-      <c r="G13" s="72" t="s">
-        <v>115</v>
-      </c>
-      <c r="H13" s="66">
+      <c r="G13" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="H13" s="19">
         <v>0.9</v>
       </c>
       <c r="I13">
@@ -3307,12 +3359,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>129</v>
+      </c>
+      <c r="C14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" t="s">
+        <v>94</v>
       </c>
       <c r="F14">
         <v>5</v>
       </c>
-      <c r="H14" s="66">
+      <c r="G14" s="21"/>
+      <c r="H14" s="19">
         <v>0.9</v>
       </c>
       <c r="I14">
@@ -3342,12 +3404,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F15">
         <v>5</v>
       </c>
-      <c r="H15" s="66">
+      <c r="G15" s="21"/>
+      <c r="H15" s="19">
         <v>0.9</v>
       </c>
       <c r="I15">
@@ -3377,12 +3440,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F16">
         <v>5</v>
       </c>
-      <c r="H16" s="66">
+      <c r="G16" s="21"/>
+      <c r="H16" s="19">
         <v>0.9</v>
       </c>
       <c r="I16">
@@ -3412,12 +3476,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F17">
         <v>5</v>
       </c>
-      <c r="H17" s="66">
+      <c r="G17" s="21"/>
+      <c r="H17" s="19">
         <v>0.9</v>
       </c>
       <c r="I17">
@@ -3447,12 +3512,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F18">
         <v>5</v>
       </c>
-      <c r="H18" s="66">
+      <c r="G18" s="21"/>
+      <c r="H18" s="19">
         <v>0.9</v>
       </c>
       <c r="I18">
@@ -3482,12 +3548,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F19">
         <v>5</v>
       </c>
-      <c r="H19" s="66">
+      <c r="G19" s="21"/>
+      <c r="H19" s="19">
         <v>0.9</v>
       </c>
       <c r="I19">
@@ -3517,12 +3584,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>135</v>
+      </c>
+      <c r="C20" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" t="s">
+        <v>94</v>
       </c>
       <c r="F20">
         <v>5</v>
       </c>
-      <c r="H20" s="66">
+      <c r="G20" s="21"/>
+      <c r="H20" s="19">
         <v>0.9</v>
       </c>
       <c r="I20">
@@ -3552,12 +3629,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>132</v>
+      </c>
+      <c r="C21" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" t="s">
+        <v>94</v>
       </c>
       <c r="F21">
         <v>5</v>
       </c>
-      <c r="H21" s="66">
+      <c r="G21" s="21"/>
+      <c r="H21" s="19">
         <v>0.9</v>
       </c>
       <c r="I21">
@@ -3605,10 +3692,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C2" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="42"/>
+      <c r="C2" s="79" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="79"/>
       <c r="E2" s="4"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
@@ -3616,7 +3703,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E3" s="4"/>
     </row>
@@ -3625,7 +3712,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E4" s="4"/>
     </row>
@@ -3634,7 +3721,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E5" s="4"/>
     </row>
@@ -3643,7 +3730,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E6" s="4"/>
     </row>
@@ -3652,242 +3739,242 @@
         <v>5</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E7" s="4"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E11" s="5">
         <v>0</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E12" s="5">
         <v>33</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K12" s="5">
         <v>17</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E13" s="5">
         <v>41</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K13" s="5">
         <v>21</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E14" s="5">
         <v>51</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K14" s="5">
         <v>26</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E15" s="5">
         <v>61</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K15" s="5">
         <v>31</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E16" s="5">
         <v>71</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K16" s="5">
         <v>36</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E17" s="5">
         <v>81</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K17" s="5">
         <v>41</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E18" s="5">
         <v>91</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K18" s="5">
         <v>45</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/marksheet.xlsx
+++ b/marksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atosh\OneDrive\Desktop\Study-Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66D2390-2F2A-4A9D-B419-82D9C36000A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78E5639-7FBC-4A7D-B946-0863A8FBC5B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReportCard" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="144">
   <si>
     <t>BGS</t>
   </si>
@@ -52,9 +52,6 @@
     <t>Sathi Sharma</t>
   </si>
   <si>
-    <t>Farjana Akther</t>
-  </si>
-  <si>
     <t>Vumi Roy</t>
   </si>
   <si>
@@ -64,9 +61,6 @@
     <t>Manik Roy</t>
   </si>
   <si>
-    <t>Chondo Roy</t>
-  </si>
-  <si>
     <t>Star Rating</t>
   </si>
   <si>
@@ -458,6 +452,27 @@
   </si>
   <si>
     <t>Simu Khatun</t>
+  </si>
+  <si>
+    <t>Chando Roy</t>
+  </si>
+  <si>
+    <t>Dina Bondhu Roy</t>
+  </si>
+  <si>
+    <t>Bobita Rani</t>
+  </si>
+  <si>
+    <t>Kanial Khata(Roy Para)</t>
+  </si>
+  <si>
+    <t>Sree Pram Kumer(Chadon)</t>
+  </si>
+  <si>
+    <t>Varoti Rani</t>
+  </si>
+  <si>
+    <t>Mst Farjana Akter</t>
   </si>
 </sst>
 </file>
@@ -829,43 +844,95 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -877,65 +944,11 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -944,41 +957,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1520,39 +1535,39 @@
     </row>
     <row r="3" spans="2:16" ht="33.75" x14ac:dyDescent="0.25">
       <c r="B3" s="9"/>
-      <c r="C3" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="54"/>
+      <c r="C3" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
       <c r="P3" s="10"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B4" s="9"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
+      <c r="D4" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
       <c r="O4" s="1"/>
       <c r="P4" s="10"/>
     </row>
@@ -1560,17 +1575,17 @@
       <c r="B5" s="9"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="57" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="56"/>
-      <c r="L5" s="56"/>
-      <c r="M5" s="56"/>
+      <c r="E5" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="10"/>
@@ -1578,19 +1593,19 @@
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="9"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
+      <c r="D6" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
       <c r="O6" s="2"/>
       <c r="P6" s="10"/>
     </row>
@@ -1600,11 +1615,11 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" s="9"/>
-      <c r="C8" s="52" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
+      <c r="C8" s="62" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1612,11 +1627,11 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
-      <c r="M8" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="N8" s="51"/>
-      <c r="O8" s="51"/>
+      <c r="M8" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" s="61"/>
+      <c r="O8" s="61"/>
       <c r="P8" s="10"/>
     </row>
     <row r="9" spans="2:16" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1638,59 +1653,59 @@
     </row>
     <row r="10" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="9"/>
-      <c r="C10" s="59" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="60"/>
-      <c r="K10" s="60"/>
-      <c r="L10" s="60"/>
-      <c r="M10" s="60"/>
-      <c r="N10" s="60"/>
-      <c r="O10" s="60"/>
+      <c r="C10" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="51"/>
+      <c r="O10" s="51"/>
       <c r="P10" s="10"/>
     </row>
     <row r="11" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="9"/>
-      <c r="C11" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="60"/>
-      <c r="K11" s="60"/>
-      <c r="L11" s="60"/>
-      <c r="M11" s="60"/>
-      <c r="N11" s="60"/>
-      <c r="O11" s="60"/>
+      <c r="C11" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="51"/>
       <c r="P11" s="10"/>
     </row>
     <row r="12" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B12" s="9"/>
-      <c r="C12" s="61" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="60"/>
-      <c r="K12" s="60"/>
-      <c r="L12" s="60"/>
-      <c r="M12" s="60"/>
-      <c r="N12" s="60"/>
-      <c r="O12" s="60"/>
+      <c r="C12" s="63" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="51"/>
+      <c r="O12" s="51"/>
       <c r="P12" s="10"/>
     </row>
     <row r="13" spans="2:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1712,69 +1727,66 @@
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B14" s="9"/>
-      <c r="C14" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="62"/>
-      <c r="E14" s="66">
-        <v>3</v>
-      </c>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
+      <c r="C14" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="64"/>
+      <c r="E14" s="42">
+        <v>11</v>
+      </c>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
-      <c r="K14" s="62" t="s">
-        <v>47</v>
-      </c>
-      <c r="L14" s="62"/>
-      <c r="M14" s="63">
+      <c r="K14" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="L14" s="64"/>
+      <c r="M14" s="65">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!K14,DataBase!$A$1:$O$1,0),0)</f>
         <v>5</v>
       </c>
-      <c r="N14" s="63"/>
-      <c r="O14" s="63"/>
+      <c r="N14" s="65"/>
+      <c r="O14" s="65"/>
       <c r="P14" s="10"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B15" s="9"/>
-      <c r="C15" s="62" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="62"/>
-      <c r="E15" s="64" t="str">
+      <c r="C15" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="64"/>
+      <c r="E15" s="43" t="str">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!C15,DataBase!$A$1:$O$1,0),0)</f>
-        <v>Imran Islam</v>
-      </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
+        <v xml:space="preserve">Md Fazle Rabbi </v>
+      </c>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
-      <c r="K15" s="62" t="s">
-        <v>49</v>
-      </c>
-      <c r="L15" s="62"/>
-      <c r="M15" s="64" t="str">
-        <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!K15,DataBase!$A$1:$O$1,0),0)</f>
-        <v>01790524726</v>
-      </c>
-      <c r="N15" s="64"/>
-      <c r="O15" s="64"/>
+      <c r="K15" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="L15" s="64"/>
+      <c r="M15" s="43"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="43"/>
       <c r="P15" s="10"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B16" s="9"/>
-      <c r="C16" s="62" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="62"/>
-      <c r="E16" s="64" t="str">
+      <c r="C16" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="64"/>
+      <c r="E16" s="43" t="str">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!C16,DataBase!$A$1:$O$1,0),0)</f>
-        <v>Ferazul Islam</v>
-      </c>
-      <c r="F16" s="64"/>
-      <c r="G16" s="64"/>
+        <v>Md Hamidul Haque</v>
+      </c>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1787,16 +1799,16 @@
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B17" s="9"/>
-      <c r="C17" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="64" t="str">
+      <c r="C17" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="41"/>
+      <c r="E17" s="43" t="str">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!C17,DataBase!$A$1:$O$1,0),0)</f>
-        <v>Rina Parvin</v>
-      </c>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
+        <v>Simu Khatun</v>
+      </c>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1809,16 +1821,16 @@
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B18" s="9"/>
-      <c r="C18" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="65"/>
-      <c r="E18" s="64" t="str">
+      <c r="C18" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="41"/>
+      <c r="E18" s="43" t="str">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(ReportCard!C18,DataBase!$A$1:$O$1,0),0)</f>
-        <v>Kanial Khata</v>
-      </c>
-      <c r="F18" s="64"/>
-      <c r="G18" s="64"/>
+        <v>Kanial Khata Cinirkuti Bazar</v>
+      </c>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -1848,334 +1860,334 @@
     </row>
     <row r="20" spans="2:16" ht="23.25" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B20" s="9"/>
-      <c r="C20" s="67" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="67"/>
-      <c r="K20" s="67"/>
-      <c r="L20" s="67"/>
-      <c r="M20" s="67"/>
-      <c r="N20" s="67"/>
-      <c r="O20" s="67"/>
+      <c r="C20" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="35"/>
       <c r="P20" s="10"/>
     </row>
     <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="9"/>
-      <c r="C21" s="68" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="69"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
-      <c r="L21" s="69"/>
-      <c r="M21" s="69"/>
-      <c r="N21" s="69"/>
-      <c r="O21" s="70"/>
+      <c r="C21" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="37"/>
+      <c r="N21" s="37"/>
+      <c r="O21" s="38"/>
       <c r="P21" s="10"/>
     </row>
     <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="9"/>
-      <c r="C22" s="48" t="s">
+      <c r="C22" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="40"/>
+      <c r="E22" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="71"/>
-      <c r="E22" s="74" t="s">
+      <c r="F22" s="29"/>
+      <c r="G22" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="H22" s="29"/>
+      <c r="I22" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="F22" s="75"/>
-      <c r="G22" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="H22" s="75"/>
-      <c r="I22" s="74" t="s">
-        <v>63</v>
-      </c>
-      <c r="J22" s="75"/>
-      <c r="K22" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="L22" s="75"/>
-      <c r="M22" s="74" t="s">
-        <v>72</v>
-      </c>
-      <c r="N22" s="77"/>
-      <c r="O22" s="75"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="L22" s="29"/>
+      <c r="M22" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="N22" s="28"/>
+      <c r="O22" s="29"/>
       <c r="P22" s="10"/>
     </row>
     <row r="23" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="9"/>
-      <c r="C23" s="72" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="73"/>
-      <c r="E23" s="32">
+      <c r="C23" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="34"/>
+      <c r="E23" s="25">
         <v>100</v>
       </c>
-      <c r="F23" s="76"/>
-      <c r="G23" s="32">
+      <c r="F23" s="26"/>
+      <c r="G23" s="25">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C23,DataBase!$A$1:$O$1,0),0)</f>
-        <v>92</v>
-      </c>
-      <c r="H23" s="76"/>
-      <c r="I23" s="29">
+        <v>80</v>
+      </c>
+      <c r="H23" s="26"/>
+      <c r="I23" s="31">
         <f>G23/E23</f>
-        <v>0.92</v>
-      </c>
-      <c r="J23" s="31"/>
-      <c r="K23" s="32" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="J23" s="32"/>
+      <c r="K23" s="25" t="str">
         <f>LOOKUP(G23,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
-        <v>A+</v>
-      </c>
-      <c r="L23" s="76"/>
-      <c r="M23" s="32" t="str">
+        <v>A-</v>
+      </c>
+      <c r="L23" s="26"/>
+      <c r="M23" s="25" t="str">
         <f>IF(I23&lt;0.33,"FAIL","PASS")</f>
         <v>PASS</v>
       </c>
-      <c r="N23" s="78"/>
-      <c r="O23" s="76"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="26"/>
       <c r="P23" s="10"/>
     </row>
     <row r="24" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="9"/>
-      <c r="C24" s="72" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="73"/>
-      <c r="E24" s="32">
+      <c r="C24" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="34"/>
+      <c r="E24" s="25">
         <v>100</v>
       </c>
-      <c r="F24" s="76"/>
-      <c r="G24" s="32">
+      <c r="F24" s="26"/>
+      <c r="G24" s="25">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C24,DataBase!$A$1:$O$1,0),0)</f>
-        <v>97</v>
-      </c>
-      <c r="H24" s="76"/>
-      <c r="I24" s="29">
+        <v>85</v>
+      </c>
+      <c r="H24" s="26"/>
+      <c r="I24" s="31">
         <f t="shared" ref="I24:I29" si="0">G24/E24</f>
-        <v>0.97</v>
-      </c>
-      <c r="J24" s="31"/>
-      <c r="K24" s="32" t="str">
+        <v>0.85</v>
+      </c>
+      <c r="J24" s="32"/>
+      <c r="K24" s="25" t="str">
         <f>LOOKUP(G24,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
-        <v>A+</v>
-      </c>
-      <c r="L24" s="76"/>
-      <c r="M24" s="32" t="str">
+        <v>A</v>
+      </c>
+      <c r="L24" s="26"/>
+      <c r="M24" s="25" t="str">
         <f t="shared" ref="M24:M29" si="1">IF(I24&lt;0.33,"FAIL","PASS")</f>
         <v>PASS</v>
       </c>
-      <c r="N24" s="78"/>
-      <c r="O24" s="76"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="26"/>
       <c r="P24" s="10"/>
     </row>
     <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="9"/>
-      <c r="C25" s="72" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="73"/>
-      <c r="E25" s="32">
+      <c r="C25" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="34"/>
+      <c r="E25" s="25">
         <v>100</v>
       </c>
-      <c r="F25" s="76"/>
-      <c r="G25" s="32">
+      <c r="F25" s="26"/>
+      <c r="G25" s="25">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C25,DataBase!$A$1:$O$1,0),0)</f>
-        <v>98</v>
-      </c>
-      <c r="H25" s="76"/>
-      <c r="I25" s="29">
+        <v>80</v>
+      </c>
+      <c r="H25" s="26"/>
+      <c r="I25" s="31">
         <f t="shared" si="0"/>
-        <v>0.98</v>
-      </c>
-      <c r="J25" s="31"/>
-      <c r="K25" s="32" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="J25" s="32"/>
+      <c r="K25" s="25" t="str">
         <f>LOOKUP(G25,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
-        <v>A+</v>
-      </c>
-      <c r="L25" s="76"/>
-      <c r="M25" s="32" t="str">
+        <v>A-</v>
+      </c>
+      <c r="L25" s="26"/>
+      <c r="M25" s="25" t="str">
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="N25" s="78"/>
-      <c r="O25" s="76"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="26"/>
       <c r="P25" s="10"/>
     </row>
     <row r="26" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="9"/>
-      <c r="C26" s="72" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="73"/>
-      <c r="E26" s="32">
+      <c r="C26" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="34"/>
+      <c r="E26" s="25">
         <v>100</v>
       </c>
-      <c r="F26" s="76"/>
-      <c r="G26" s="32">
+      <c r="F26" s="26"/>
+      <c r="G26" s="25">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C26,DataBase!$A$1:$O$1,0),0)</f>
-        <v>85</v>
-      </c>
-      <c r="H26" s="76"/>
-      <c r="I26" s="29">
+        <v>84</v>
+      </c>
+      <c r="H26" s="26"/>
+      <c r="I26" s="31">
         <f t="shared" si="0"/>
-        <v>0.85</v>
-      </c>
-      <c r="J26" s="31"/>
-      <c r="K26" s="32" t="str">
+        <v>0.84</v>
+      </c>
+      <c r="J26" s="32"/>
+      <c r="K26" s="25" t="str">
         <f>LOOKUP(G26,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
         <v>A</v>
       </c>
-      <c r="L26" s="76"/>
-      <c r="M26" s="32" t="str">
+      <c r="L26" s="26"/>
+      <c r="M26" s="25" t="str">
         <f>IF(I26&lt;0.33,"FAIL","PASS")</f>
         <v>PASS</v>
       </c>
-      <c r="N26" s="78"/>
-      <c r="O26" s="76"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="26"/>
       <c r="P26" s="10"/>
     </row>
     <row r="27" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="9"/>
-      <c r="C27" s="72" t="s">
+      <c r="C27" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="D27" s="73"/>
-      <c r="E27" s="32">
+      <c r="D27" s="34"/>
+      <c r="E27" s="25">
         <v>100</v>
       </c>
-      <c r="F27" s="76"/>
-      <c r="G27" s="32">
+      <c r="F27" s="26"/>
+      <c r="G27" s="25">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C27,DataBase!$A$1:$O$1,0),0)</f>
-        <v>94</v>
-      </c>
-      <c r="H27" s="76"/>
-      <c r="I27" s="29">
+        <v>80</v>
+      </c>
+      <c r="H27" s="26"/>
+      <c r="I27" s="31">
         <f t="shared" si="0"/>
-        <v>0.94</v>
-      </c>
-      <c r="J27" s="31"/>
-      <c r="K27" s="32" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="J27" s="32"/>
+      <c r="K27" s="25" t="str">
         <f>LOOKUP(G27,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
-        <v>A+</v>
-      </c>
-      <c r="L27" s="76"/>
-      <c r="M27" s="32" t="str">
+        <v>A-</v>
+      </c>
+      <c r="L27" s="26"/>
+      <c r="M27" s="25" t="str">
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="N27" s="78"/>
-      <c r="O27" s="76"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="26"/>
       <c r="P27" s="10"/>
     </row>
     <row r="28" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="9"/>
-      <c r="C28" s="72" t="s">
-        <v>55</v>
-      </c>
-      <c r="D28" s="73"/>
-      <c r="E28" s="32">
+      <c r="C28" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" s="34"/>
+      <c r="E28" s="25">
         <v>100</v>
       </c>
-      <c r="F28" s="76"/>
-      <c r="G28" s="32">
+      <c r="F28" s="26"/>
+      <c r="G28" s="25">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C28,DataBase!$A$1:$O$1,0),0)</f>
-        <v>95</v>
-      </c>
-      <c r="H28" s="76"/>
-      <c r="I28" s="29">
+        <v>82</v>
+      </c>
+      <c r="H28" s="26"/>
+      <c r="I28" s="31">
         <f t="shared" si="0"/>
-        <v>0.95</v>
-      </c>
-      <c r="J28" s="31"/>
-      <c r="K28" s="32" t="str">
+        <v>0.82</v>
+      </c>
+      <c r="J28" s="32"/>
+      <c r="K28" s="25" t="str">
         <f>LOOKUP(G28,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
-        <v>A+</v>
-      </c>
-      <c r="L28" s="76"/>
-      <c r="M28" s="32" t="str">
+        <v>A</v>
+      </c>
+      <c r="L28" s="26"/>
+      <c r="M28" s="25" t="str">
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="N28" s="78"/>
-      <c r="O28" s="76"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="26"/>
       <c r="P28" s="10"/>
     </row>
     <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="9"/>
-      <c r="C29" s="72" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" s="73"/>
-      <c r="E29" s="32">
+      <c r="C29" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="34"/>
+      <c r="E29" s="25">
         <v>50</v>
       </c>
-      <c r="F29" s="76"/>
-      <c r="G29" s="32">
+      <c r="F29" s="26"/>
+      <c r="G29" s="25">
         <f>VLOOKUP($E$14,DataBase!$A$2:$O$21,MATCH(C29,DataBase!$A$1:$O$1,0),0)</f>
-        <v>46</v>
-      </c>
-      <c r="H29" s="76"/>
-      <c r="I29" s="29">
+        <v>45</v>
+      </c>
+      <c r="H29" s="26"/>
+      <c r="I29" s="31">
         <f t="shared" si="0"/>
-        <v>0.92</v>
-      </c>
-      <c r="J29" s="31"/>
-      <c r="K29" s="32" t="str">
+        <v>0.9</v>
+      </c>
+      <c r="J29" s="32"/>
+      <c r="K29" s="25" t="str">
         <f>LOOKUP(G29,Rating!$K$11:$K$18,Rating!$L$11:$L$18)</f>
         <v>A+</v>
       </c>
-      <c r="L29" s="76"/>
-      <c r="M29" s="32" t="str">
+      <c r="L29" s="26"/>
+      <c r="M29" s="25" t="str">
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="N29" s="78"/>
-      <c r="O29" s="76"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="26"/>
       <c r="P29" s="10"/>
     </row>
     <row r="30" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="9"/>
-      <c r="C30" s="72" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="73"/>
-      <c r="E30" s="32">
+      <c r="C30" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="34"/>
+      <c r="E30" s="25">
         <f>SUM(E23:F29)</f>
         <v>650</v>
       </c>
-      <c r="F30" s="76"/>
-      <c r="G30" s="32">
+      <c r="F30" s="26"/>
+      <c r="G30" s="25">
         <f>SUM(G23:H29)</f>
-        <v>607</v>
-      </c>
-      <c r="H30" s="76"/>
-      <c r="I30" s="29">
+        <v>536</v>
+      </c>
+      <c r="H30" s="26"/>
+      <c r="I30" s="31">
         <f>G30/E30</f>
-        <v>0.93384615384615388</v>
-      </c>
-      <c r="J30" s="31"/>
-      <c r="K30" s="32" t="str">
+        <v>0.82461538461538464</v>
+      </c>
+      <c r="J30" s="32"/>
+      <c r="K30" s="25" t="str">
         <f>LOOKUP(I30*100,Rating!$E$11:$E$18,Rating!$F$11:$F$18)</f>
-        <v>A+</v>
-      </c>
-      <c r="L30" s="76"/>
-      <c r="M30" s="32" t="str">
+        <v>A</v>
+      </c>
+      <c r="L30" s="26"/>
+      <c r="M30" s="25" t="str">
         <f t="shared" ref="M30" si="2">IF(I30&lt;0.33,"FAIL","PASS")</f>
         <v>PASS</v>
       </c>
-      <c r="N30" s="78"/>
-      <c r="O30" s="76"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="26"/>
       <c r="P30" s="10"/>
     </row>
     <row r="31" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2197,155 +2209,155 @@
     </row>
     <row r="32" spans="2:16" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B32" s="9"/>
-      <c r="C32" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
+      <c r="C32" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
       <c r="F32" s="18">
         <v>5</v>
       </c>
-      <c r="G32" s="44" t="str">
+      <c r="G32" s="52" t="str">
         <f>REPT("⭐",F32)</f>
         <v>⭐⭐⭐⭐⭐</v>
       </c>
-      <c r="H32" s="44"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="44"/>
-      <c r="K32" s="44"/>
-      <c r="L32" s="44"/>
-      <c r="M32" s="44"/>
-      <c r="N32" s="44"/>
-      <c r="O32" s="45"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="52"/>
+      <c r="M32" s="52"/>
+      <c r="N32" s="52"/>
+      <c r="O32" s="53"/>
       <c r="P32" s="10"/>
     </row>
     <row r="33" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="9"/>
-      <c r="C33" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="D33" s="49"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="49"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="49"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="49"/>
-      <c r="K33" s="49"/>
-      <c r="L33" s="49"/>
-      <c r="M33" s="49"/>
-      <c r="N33" s="49"/>
-      <c r="O33" s="50"/>
+      <c r="C33" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="56"/>
+      <c r="K33" s="56"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="56"/>
+      <c r="N33" s="56"/>
+      <c r="O33" s="57"/>
       <c r="P33" s="10"/>
     </row>
     <row r="34" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B34" s="9"/>
-      <c r="C34" s="38" t="str">
+      <c r="C34" s="58" t="str">
         <f>REPT("⭐",1)</f>
         <v>⭐</v>
       </c>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="K34" s="42"/>
-      <c r="L34" s="42"/>
-      <c r="M34" s="42"/>
-      <c r="N34" s="42"/>
-      <c r="O34" s="43"/>
+      <c r="D34" s="59"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="59"/>
+      <c r="I34" s="60"/>
+      <c r="J34" s="66" t="s">
+        <v>7</v>
+      </c>
+      <c r="K34" s="67"/>
+      <c r="L34" s="67"/>
+      <c r="M34" s="67"/>
+      <c r="N34" s="67"/>
+      <c r="O34" s="68"/>
       <c r="P34" s="10"/>
     </row>
     <row r="35" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="9"/>
-      <c r="C35" s="38" t="str">
+      <c r="C35" s="58" t="str">
         <f>REPT("⭐",2)</f>
         <v>⭐⭐</v>
       </c>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="K35" s="42"/>
-      <c r="L35" s="42"/>
-      <c r="M35" s="42"/>
-      <c r="N35" s="42"/>
-      <c r="O35" s="43"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="60"/>
+      <c r="J35" s="66" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="67"/>
+      <c r="L35" s="67"/>
+      <c r="M35" s="67"/>
+      <c r="N35" s="67"/>
+      <c r="O35" s="68"/>
       <c r="P35" s="10"/>
     </row>
     <row r="36" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B36" s="9"/>
-      <c r="C36" s="38" t="str">
+      <c r="C36" s="58" t="str">
         <f>REPT("⭐",3)</f>
         <v>⭐⭐⭐</v>
       </c>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="43"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="60"/>
+      <c r="J36" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="K36" s="67"/>
+      <c r="L36" s="67"/>
+      <c r="M36" s="67"/>
+      <c r="N36" s="67"/>
+      <c r="O36" s="68"/>
       <c r="P36" s="10"/>
     </row>
     <row r="37" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="9"/>
-      <c r="C37" s="38" t="str">
+      <c r="C37" s="58" t="str">
         <f>REPT("⭐",4)</f>
         <v>⭐⭐⭐⭐</v>
       </c>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="39"/>
-      <c r="H37" s="39"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="K37" s="42"/>
-      <c r="L37" s="42"/>
-      <c r="M37" s="42"/>
-      <c r="N37" s="42"/>
-      <c r="O37" s="43"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="K37" s="67"/>
+      <c r="L37" s="67"/>
+      <c r="M37" s="67"/>
+      <c r="N37" s="67"/>
+      <c r="O37" s="68"/>
       <c r="P37" s="10"/>
     </row>
     <row r="38" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B38" s="9"/>
-      <c r="C38" s="38" t="str">
+      <c r="C38" s="58" t="str">
         <f>REPT("⭐",5)</f>
         <v>⭐⭐⭐⭐⭐</v>
       </c>
-      <c r="D38" s="39"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="K38" s="42"/>
-      <c r="L38" s="42"/>
-      <c r="M38" s="42"/>
-      <c r="N38" s="42"/>
-      <c r="O38" s="43"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="59"/>
+      <c r="H38" s="59"/>
+      <c r="I38" s="60"/>
+      <c r="J38" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="K38" s="67"/>
+      <c r="L38" s="67"/>
+      <c r="M38" s="67"/>
+      <c r="N38" s="67"/>
+      <c r="O38" s="68"/>
       <c r="P38" s="10"/>
     </row>
     <row r="39" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2367,18 +2379,18 @@
     </row>
     <row r="40" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="9"/>
-      <c r="C40" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="29">
+      <c r="C40" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" s="72"/>
+      <c r="E40" s="72"/>
+      <c r="F40" s="72"/>
+      <c r="G40" s="72"/>
+      <c r="H40" s="31">
         <v>0.9</v>
       </c>
-      <c r="I40" s="30"/>
-      <c r="J40" s="31"/>
+      <c r="I40" s="73"/>
+      <c r="J40" s="32"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -2422,26 +2434,26 @@
     </row>
     <row r="43" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="9"/>
-      <c r="C43" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="D43" s="36"/>
-      <c r="E43" s="32" t="s">
+      <c r="C43" s="76" t="s">
+        <v>76</v>
+      </c>
+      <c r="D43" s="77"/>
+      <c r="E43" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="F43" s="74"/>
+      <c r="G43" s="75"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="76" t="s">
         <v>77</v>
       </c>
-      <c r="F43" s="33"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="J43" s="37"/>
-      <c r="K43" s="37"/>
-      <c r="L43" s="37"/>
-      <c r="M43" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="N43" s="26"/>
+      <c r="J43" s="78"/>
+      <c r="K43" s="78"/>
+      <c r="L43" s="78"/>
+      <c r="M43" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="N43" s="70"/>
       <c r="O43" s="20"/>
       <c r="P43" s="10"/>
     </row>
@@ -2600,73 +2612,21 @@
     </row>
   </sheetData>
   <mergeCells count="98">
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="M27:O27"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C20:O20"/>
-    <mergeCell ref="C21:O21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="C3:O3"/>
-    <mergeCell ref="D4:N4"/>
-    <mergeCell ref="E5:M5"/>
-    <mergeCell ref="D6:N6"/>
-    <mergeCell ref="C10:O10"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="C36:I36"/>
+    <mergeCell ref="C37:I37"/>
+    <mergeCell ref="C38:I38"/>
+    <mergeCell ref="J34:O34"/>
+    <mergeCell ref="J35:O35"/>
+    <mergeCell ref="J36:O36"/>
+    <mergeCell ref="J37:O37"/>
+    <mergeCell ref="J38:O38"/>
     <mergeCell ref="G32:O32"/>
     <mergeCell ref="C32:E32"/>
     <mergeCell ref="C33:O33"/>
@@ -2683,21 +2643,73 @@
     <mergeCell ref="M15:O15"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C35:I35"/>
-    <mergeCell ref="C36:I36"/>
-    <mergeCell ref="C37:I37"/>
-    <mergeCell ref="C38:I38"/>
-    <mergeCell ref="J34:O34"/>
-    <mergeCell ref="J35:O35"/>
-    <mergeCell ref="J36:O36"/>
-    <mergeCell ref="J37:O37"/>
-    <mergeCell ref="J38:O38"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="C3:O3"/>
+    <mergeCell ref="D4:N4"/>
+    <mergeCell ref="E5:M5"/>
+    <mergeCell ref="D6:N6"/>
+    <mergeCell ref="C10:O10"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="C20:O20"/>
+    <mergeCell ref="C21:O21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="K29:L29"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F32" xr:uid="{25D160CD-41E1-400F-8FC6-9677D68E1D32}">
@@ -2732,7 +2744,7 @@
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
@@ -2749,49 +2761,49 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" t="s">
         <v>48</v>
       </c>
-      <c r="B1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>49</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>50</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>51</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>52</v>
-      </c>
-      <c r="K1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L1" t="s">
-        <v>54</v>
       </c>
       <c r="M1" t="s">
         <v>0</v>
       </c>
       <c r="N1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -2799,22 +2811,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" t="s">
         <v>80</v>
       </c>
-      <c r="C2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" t="s">
-        <v>82</v>
-      </c>
       <c r="E2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F2">
         <v>5</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H2" s="19">
         <v>0.9</v>
@@ -2846,22 +2858,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" t="s">
         <v>84</v>
       </c>
-      <c r="C3" t="s">
-        <v>86</v>
-      </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H3" s="19">
         <v>0.9</v>
@@ -2896,19 +2908,19 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E4" t="s">
         <v>125</v>
-      </c>
-      <c r="D4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E4" t="s">
-        <v>127</v>
       </c>
       <c r="F4">
         <v>5</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H4" s="19">
         <v>0.9</v>
@@ -2940,16 +2952,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" t="s">
         <v>88</v>
       </c>
-      <c r="C5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" t="s">
-        <v>90</v>
-      </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2985,22 +2997,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" t="s">
         <v>112</v>
       </c>
-      <c r="C6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" t="s">
-        <v>114</v>
-      </c>
       <c r="E6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F6">
         <v>5</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H6" s="19">
         <v>0.9</v>
@@ -3032,22 +3044,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" t="s">
         <v>121</v>
       </c>
-      <c r="C7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" t="s">
-        <v>123</v>
-      </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H7" s="19">
         <v>0.9</v>
@@ -3079,22 +3091,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" t="s">
         <v>116</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>117</v>
-      </c>
-      <c r="D8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8" t="s">
-        <v>119</v>
       </c>
       <c r="F8">
         <v>5</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H8" s="19">
         <v>0.9</v>
@@ -3129,19 +3141,19 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" t="s">
         <v>103</v>
-      </c>
-      <c r="D9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E9" t="s">
-        <v>105</v>
       </c>
       <c r="F9">
         <v>5</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H9" s="19">
         <v>0.9</v>
@@ -3173,22 +3185,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="E10" t="s">
         <v>99</v>
-      </c>
-      <c r="D10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" t="s">
-        <v>101</v>
       </c>
       <c r="F10">
         <v>5</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H10" s="19">
         <v>0.9</v>
@@ -3220,22 +3232,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s">
         <v>91</v>
       </c>
-      <c r="C11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>93</v>
-      </c>
-      <c r="E11" t="s">
-        <v>95</v>
       </c>
       <c r="F11">
         <v>5</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H11" s="19">
         <v>0.9</v>
@@ -3267,16 +3279,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" t="s">
         <v>136</v>
       </c>
-      <c r="C12" t="s">
-        <v>137</v>
-      </c>
-      <c r="D12" t="s">
-        <v>138</v>
-      </c>
       <c r="E12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3312,22 +3324,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" t="s">
         <v>107</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>108</v>
-      </c>
-      <c r="D13" t="s">
-        <v>109</v>
-      </c>
-      <c r="E13" t="s">
-        <v>110</v>
       </c>
       <c r="F13">
         <v>5</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H13" s="19">
         <v>0.9</v>
@@ -3359,16 +3371,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" t="s">
         <v>129</v>
       </c>
-      <c r="C14" t="s">
-        <v>130</v>
-      </c>
-      <c r="D14" t="s">
-        <v>131</v>
-      </c>
       <c r="E14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3404,7 +3416,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>143</v>
+      </c>
+      <c r="C15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" t="s">
+        <v>92</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -3440,7 +3461,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" t="s">
+        <v>142</v>
+      </c>
+      <c r="E16" t="s">
+        <v>140</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -3476,7 +3506,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -3512,7 +3542,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -3548,7 +3578,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>137</v>
+      </c>
+      <c r="C19" t="s">
+        <v>138</v>
+      </c>
+      <c r="D19" t="s">
+        <v>139</v>
+      </c>
+      <c r="E19" t="s">
+        <v>140</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -3584,16 +3623,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C20" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -3629,16 +3668,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>130</v>
+      </c>
+      <c r="C21" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" t="s">
         <v>132</v>
       </c>
-      <c r="C21" t="s">
-        <v>133</v>
-      </c>
-      <c r="D21" t="s">
-        <v>134</v>
-      </c>
       <c r="E21" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -3671,6 +3710,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3693,7 +3733,7 @@
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C2" s="79" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2" s="79"/>
       <c r="E2" s="4"/>
@@ -3703,7 +3743,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E3" s="4"/>
     </row>
@@ -3712,7 +3752,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E4" s="4"/>
     </row>
@@ -3721,7 +3761,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" s="4"/>
     </row>
@@ -3730,7 +3770,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E6" s="4"/>
     </row>
@@ -3739,242 +3779,242 @@
         <v>5</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E7" s="4"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E11" s="5">
         <v>0</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E12" s="5">
         <v>33</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K12" s="5">
         <v>17</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E13" s="5">
         <v>41</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K13" s="5">
         <v>21</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E14" s="5">
         <v>51</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K14" s="5">
         <v>26</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E15" s="5">
         <v>61</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K15" s="5">
         <v>31</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E16" s="5">
         <v>71</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K16" s="5">
         <v>36</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E17" s="5">
         <v>81</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K17" s="5">
         <v>41</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E18" s="5">
         <v>91</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K18" s="5">
         <v>45</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
